--- a/examples/KID.OL/KID.OL_model.xlsx
+++ b/examples/KID.OL/KID.OL_model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/425ed27e3db279b7/Desktop/Private prosjekter/equity-research-engine/output/KID.OL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F2A547867C17545E85962F2F5B8C00B1A1DD88B5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_C03EC79B46F13208F58D021590E41B3D487AD696" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,12 +42,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="279">
   <si>
     <t>Kid ASA (KID.OL) – valuation model</t>
   </si>
   <si>
-    <t>Generated by Equity Research Engine on 2026-09-21</t>
+    <t>Generated by Equity Research Engine on 2026-09-23</t>
   </si>
   <si>
     <t>Share price (NOK)</t>
@@ -140,54 +140,69 @@
     <t>Net debt</t>
   </si>
   <si>
-    <t>Latest balance sheet (ex leases)</t>
+    <t>Balance sheet 30.06.2026 (ex leases)</t>
   </si>
   <si>
     <t>Minority interest</t>
   </si>
   <si>
+    <t>Balance sheet 30.06.2026</t>
+  </si>
+  <si>
+    <t>Tax rate</t>
+  </si>
+  <si>
+    <t>config</t>
+  </si>
+  <si>
+    <t>Config</t>
+  </si>
+  <si>
+    <t>Risk-free rate</t>
+  </si>
+  <si>
+    <t>Equity risk premium</t>
+  </si>
+  <si>
+    <t>Beta (adjusted)</t>
+  </si>
+  <si>
+    <t>Yahoo Finance (5y monthly); regression vs OSEBX rejected (R2=0.03 &lt; 0.10), Blume-adjusted</t>
+  </si>
+  <si>
+    <t>Size premium</t>
+  </si>
+  <si>
+    <t>size premium 1.50% (market cap USD 0.5bn)</t>
+  </si>
+  <si>
+    <t>Cost of debt (pre-tax)</t>
+  </si>
+  <si>
+    <t>interest expense / average debt</t>
+  </si>
+  <si>
+    <t>Gross debt for WACC weights</t>
+  </si>
+  <si>
     <t>Latest balance sheet</t>
   </si>
   <si>
-    <t>Tax rate</t>
-  </si>
-  <si>
-    <t>config</t>
-  </si>
-  <si>
-    <t>Config</t>
-  </si>
-  <si>
-    <t>Risk-free rate</t>
-  </si>
-  <si>
-    <t>Equity risk premium</t>
-  </si>
-  <si>
-    <t>Beta (adjusted)</t>
-  </si>
-  <si>
-    <t>Yahoo Finance (5y monthly); regression vs OSEBX rejected (R2=0.03 &lt; 0.10), Blume-adjusted</t>
-  </si>
-  <si>
-    <t>Size premium</t>
-  </si>
-  <si>
-    <t>size premium 1.50% (market cap USD 0.5bn)</t>
-  </si>
-  <si>
-    <t>Cost of debt (pre-tax)</t>
-  </si>
-  <si>
-    <t>interest expense / average debt</t>
-  </si>
-  <si>
-    <t>Gross debt for WACC weights</t>
-  </si>
-  <si>
     <t>Mid-year convention (1 = yes)</t>
   </si>
   <si>
+    <t>Years from FY-end to valuation date</t>
+  </si>
+  <si>
+    <t>Valuation date 23.09.2026; last fiscal year-end 31.12.2025</t>
+  </si>
+  <si>
+    <t>Years from FY-end to balance sheet</t>
+  </si>
+  <si>
+    <t>Net debt as at 30.06.2026: year-1 cash flow before that date is already in net debt</t>
+  </si>
+  <si>
     <t>Terminal method (1 = value driver)</t>
   </si>
   <si>
@@ -203,7 +218,7 @@
     <t>Expected dividend per share (NOK)</t>
   </si>
   <si>
-    <t>Last year's cash dividend per share</t>
+    <t>Indicated annual dividend (Yahoo Finance)</t>
   </si>
   <si>
     <t>Roll-forward months</t>
@@ -269,7 +284,7 @@
     <t>Net working capital % of revenue</t>
   </si>
   <si>
-    <t>Notes: Revenue growth anchored on consensus (4 analysts), fading linearly to 2.0% terminal growth. EBITDA margin held near the 3-year average of 15.3%. Net working capital held at 3.9% of revenue (3-year average from the balance sheet). Capex normalises from 5.6% to 3.6% of revenue (D&amp;A x 1.05) by 2031E.</t>
+    <t>Notes: Revenue growth anchored on consensus (4 analysts), fading linearly to 2.0% terminal growth. EBITDA margin held near the 3-year average of 15.3%. 2026E at the nowcast margin of 13.1% 2026E built on 2 reported quarters to Jun 2026: year-to-date revenue +8.1% at a 9.0% EBITDA margin (8.2% a year earlier); the remaining quarters at +7.2% growth (consensus growth for the year) and last year's seasonal margins plus the +0.8pp year-to-date margin change. Net working capital held at 3.9% of revenue (3-year average from the balance sheet). Capex normalises from 5.6% to 3.6% of revenue (D&amp;A x 1.05) by 2031E.</t>
   </si>
   <si>
     <t>Lease treatment: operating (lease rate 4.50%). Growth anchor: consensus (4 analysts).</t>
@@ -407,6 +422,21 @@
     <t>Weight of debt</t>
   </si>
   <si>
+    <t>Cross-check: bottom-up beta from the peer group (Hamada, tax at the corporate rate)</t>
+  </si>
+  <si>
+    <t>Median unlevered peer beta</t>
+  </si>
+  <si>
+    <t>Relevered at the target's D/E of 0.15</t>
+  </si>
+  <si>
+    <t>Blume-adjusted (compare with B6)</t>
+  </si>
+  <si>
+    <t>Peers with a usable beta</t>
+  </si>
+  <si>
     <t>Kid ASA – DCF valuation (NOKm)</t>
   </si>
   <si>
@@ -416,13 +446,13 @@
     <t>Year</t>
   </si>
   <si>
-    <t>Discount period (years)</t>
+    <t>Discount period (years from valuation date)</t>
   </si>
   <si>
     <t>Discount factor</t>
   </si>
   <si>
-    <t>PV of FCF</t>
+    <t>PV of FCF (year 1: after the balance-sheet date)</t>
   </si>
   <si>
     <t>Sum of PV of FCF</t>
@@ -533,7 +563,7 @@
     <t>Peer multiples</t>
   </si>
   <si>
-    <t>Multiples computed from last reported fiscal year; EV on the same lease basis as the target company.</t>
+    <t>LTM figures where the quarters are reported (else the last fiscal year); EV = market cap today + latest net debt, same lease basis as the target company; P/E on trailing twelve-month EPS.</t>
   </si>
   <si>
     <t>Company</t>
@@ -566,7 +596,34 @@
     <t>P/E</t>
   </si>
   <si>
-    <t>P/E (fwd)</t>
+    <t>P/E (NTM)</t>
+  </si>
+  <si>
+    <t>EV/Sales (NTM)</t>
+  </si>
+  <si>
+    <t>EV/EBITDA (NTM*)</t>
+  </si>
+  <si>
+    <t>P/E (FY0)</t>
+  </si>
+  <si>
+    <t>P/E (FY1)</t>
+  </si>
+  <si>
+    <t>Growth FY1</t>
+  </si>
+  <si>
+    <t>EPS growth</t>
+  </si>
+  <si>
+    <t>PEG</t>
+  </si>
+  <si>
+    <t>FCF yield</t>
+  </si>
+  <si>
+    <t>Div. yield</t>
   </si>
   <si>
     <t>Europris</t>
@@ -653,16 +710,55 @@
     <t>Market cap</t>
   </si>
   <si>
-    <t>LTM revenue</t>
-  </si>
-  <si>
-    <t>LTM EBITDA</t>
-  </si>
-  <si>
-    <t>LTM EBIT</t>
-  </si>
-  <si>
-    <t>LTM EPS</t>
+    <t>Revenue (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EBITDA (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EBIT (LTM Jun 2026)</t>
+  </si>
+  <si>
+    <t>EPS, trailing 12 months (NOK)</t>
+  </si>
+  <si>
+    <t>Income figures: FY2025 + 2 quarter(s) to Jun 2026 - same quarter(s) of 2025. Net debt: balance sheet 30.06.2026. EPS: Yahoo Finance trailing twelve months, the same basis as the peers' P/E. * EV/EBITDA (NTM) = EV over NTM consensus revenue at the LTM margin (no EBITDA consensus on Yahoo).</t>
+  </si>
+  <si>
+    <t>EV/EBITDA regression on the peers above (engine OLS with an intercept; coefficients are inputs, the fitted value is live)</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>Coefficient: expected revenue growth</t>
+  </si>
+  <si>
+    <t>Coefficient: EBITDA margin</t>
+  </si>
+  <si>
+    <t>R²</t>
+  </si>
+  <si>
+    <t>Residual standard deviation (x)</t>
+  </si>
+  <si>
+    <t>Peers in the regression</t>
+  </si>
+  <si>
+    <t>Kid expected revenue growth</t>
+  </si>
+  <si>
+    <t>Kid EBITDA margin (LTM)</t>
+  </si>
+  <si>
+    <t>Fitted EV/EBITDA</t>
+  </si>
+  <si>
+    <t>R² 0.61: used as a football-field bar (±1 residual standard deviation)</t>
+  </si>
+  <si>
+    <t>Regression-implied value per share (NOK)</t>
   </si>
   <si>
     <t>Valuation summary</t>
@@ -696,6 +792,9 @@
   </si>
   <si>
     <t>P/E (peer 25th–75th pct)</t>
+  </si>
+  <si>
+    <t>EV/EBITDA regression (growth, margin ±1σ)</t>
   </si>
   <si>
     <t>Model integrity checks</t>
@@ -792,8 +891,8 @@
     <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0.0\);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="0.0&quot;x&quot;"/>
-    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="170" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -857,13 +956,13 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF008000"/>
+      <color rgb="FF003255"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FF003255"/>
+      <color rgb="FF008000"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -911,7 +1010,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -920,8 +1019,8 @@
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -939,21 +1038,21 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -968,15 +1067,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1055,9 +1155,9 @@
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Football field'!$A$5:$A$9</c:f>
+              <c:f>'Football field'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>52-week range</c:v>
                 </c:pt>
@@ -1073,36 +1173,42 @@
                 <c:pt idx="4">
                   <c:v>P/E (peer 25th–75th pct)</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>EV/EBITDA regression (growth, margin ±1σ)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Football field'!$B$5:$B$9</c:f>
+              <c:f>'Football field'!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>112</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>112.18979017657526</c:v>
+                  <c:v>110.24282513046317</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>82.781109499011663</c:v>
+                  <c:v>91.880634713441381</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>86.761242532191645</c:v>
+                  <c:v>95.321687373234155</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>83.867744700000003</c:v>
+                  <c:v>97.002672929999989</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>104.41356756861812</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EC74-4CC3-AF40-599560803D34}"/>
+              <c16:uniqueId val="{00000000-7BBF-4348-A86A-1B1BFD4405B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1131,9 +1237,9 @@
           <c:invertIfNegative val="1"/>
           <c:cat>
             <c:strRef>
-              <c:f>'Football field'!$A$5:$A$9</c:f>
+              <c:f>'Football field'!$A$5:$A$10</c:f>
               <c:strCache>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>52-week range</c:v>
                 </c:pt>
@@ -1149,29 +1255,35 @@
                 <c:pt idx="4">
                   <c:v>P/E (peer 25th–75th pct)</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>EV/EBITDA regression (growth, margin ±1σ)</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Football field'!$D$5:$D$9</c:f>
+              <c:f>'Football field'!$D$5:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0.00;\(#,##0.00\);"-"</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="6"/>
                 <c:pt idx="0">
                   <c:v>42.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32.821585365856095</c:v>
+                  <c:v>33.85746507989181</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38.115190999336562</c:v>
+                  <c:v>19.572562907555053</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>26.739720359858367</c:v>
+                  <c:v>21.724436273584161</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.197616079999975</c:v>
+                  <c:v>42.020825310000021</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>39.422219420604179</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1190,7 +1302,7 @@
               </c14:invertSolidFillFmt>
             </c:ext>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-EC74-4CC3-AF40-599560803D34}"/>
+              <c16:uniqueId val="{00000001-7BBF-4348-A86A-1B1BFD4405B7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1599,7 +1711,7 @@
       </c>
       <c r="B4" s="4">
         <f>Inputs!$B$5</f>
-        <v>118.8</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1608,7 +1720,7 @@
       </c>
       <c r="B5" s="4">
         <f>DCF!B21</f>
-        <v>126.74135132201357</v>
+        <v>125.25515303813016</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1617,7 +1729,7 @@
       </c>
       <c r="B6" s="4">
         <f>Scenarios!$I$8</f>
-        <v>130.91670532206183</v>
+        <v>129.59675408012021</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1626,7 +1738,7 @@
       </c>
       <c r="B7" s="4">
         <f>DCF!B30</f>
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1635,7 +1747,7 @@
       </c>
       <c r="B8" s="5">
         <f>DCF!B31</f>
-        <v>9.4276094276094291E-2</v>
+        <v>3.1096563011456579E-2</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1644,7 +1756,7 @@
       </c>
       <c r="B9" s="5">
         <f>DCF!B32</f>
-        <v>0.15740746643017389</v>
+        <v>0.11292962356792136</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -1653,7 +1765,7 @@
       </c>
       <c r="B10" s="6" t="str">
         <f>DCF!B33</f>
-        <v>BUY</v>
+        <v>HOLD</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -1671,7 +1783,7 @@
       </c>
       <c r="B12" s="7">
         <f>WACC!$B$17</f>
-        <v>8.5945104064214434E-2</v>
+        <v>8.6002147683209157E-2</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -1689,7 +1801,7 @@
       </c>
       <c r="B14" s="8">
         <f>Peers!E22</f>
-        <v>11.447929089466596</v>
+        <v>11.874442747609255</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -1698,7 +1810,7 @@
       </c>
       <c r="B15" s="8">
         <f>Peers!F22</f>
-        <v>9.8113677989749704</v>
+        <v>10.473950952549995</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
@@ -1753,162 +1865,162 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>218</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>219</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>220</v>
+        <v>253</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>221</v>
+        <v>254</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>222</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B5" s="53" t="b">
+        <v>256</v>
+      </c>
+      <c r="B5" s="54" t="b">
         <f>WACC!$B$17&gt;Inputs!$B$11</f>
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B6" s="53" t="b">
+        <v>258</v>
+      </c>
+      <c r="B6" s="54" t="b">
         <f>ABS(DCF!B16-(DCF!B10+DCF!B15))&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" s="53" t="b">
+        <v>260</v>
+      </c>
+      <c r="B7" s="54" t="b">
         <f>ABS(DCF!B19-(DCF!B16-Inputs!$B$8-Inputs!$B$9))&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="53" t="b">
+        <v>262</v>
+      </c>
+      <c r="B8" s="54" t="b">
         <f>ABS(DCF!E41-DCF!B21)&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>230</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="B9" s="53" t="b">
+        <v>264</v>
+      </c>
+      <c r="B9" s="54" t="b">
         <f>ABS(Scenarios!I6-DCF!B21)&lt;0.01</f>
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>232</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>233</v>
-      </c>
-      <c r="B10" s="53" t="b">
+        <v>266</v>
+      </c>
+      <c r="B10" s="54" t="b">
         <f>Forecast!B6=Historicals!E5</f>
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>234</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="B11" s="53" t="b">
+        <v>268</v>
+      </c>
+      <c r="B11" s="54" t="b">
         <f>ABS(WACC!B15+WACC!B16-1)&lt;0.000001</f>
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>236</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B12" s="53" t="b">
+        <v>270</v>
+      </c>
+      <c r="B12" s="54" t="b">
         <f>ABS(Scenarios!B8-1)&lt;0.000001</f>
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>238</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B13" s="53" t="b">
+        <v>272</v>
+      </c>
+      <c r="B13" s="54" t="b">
         <f>AND(Inputs!$B$5&gt;0,Inputs!$B$7&gt;0,Inputs!$B$6&gt;0)</f>
         <v>1</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>240</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B14" s="53" t="b">
+        <v>274</v>
+      </c>
+      <c r="B14" s="54" t="b">
         <f>DCF!B24&lt;0.85</f>
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>242</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B15" s="53" t="b">
+        <v>276</v>
+      </c>
+      <c r="B15" s="54" t="b">
         <f>SUMPRODUCT(--ISERROR(Forecast!B5:I20))+SUMPRODUCT(--ISERROR(DCF!B5:G33))+SUMPRODUCT(--ISERROR(Scenarios!B5:J8))=0</f>
         <v>1</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="B17" s="54" t="str">
+        <v>278</v>
+      </c>
+      <c r="B17" s="55" t="str">
         <f>IF(AND(B5:B15),"ALL OK","CHECK")</f>
         <v>ALL OK</v>
       </c>
@@ -1920,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1953,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="15">
-        <v>118.8</v>
+        <v>122.2</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>26</v>
@@ -1986,7 +2098,7 @@
         <v>31</v>
       </c>
       <c r="B8" s="18">
-        <v>722.37199999999996</v>
+        <v>1081.2090000000001</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>32</v>
@@ -2088,12 +2200,12 @@
         <v>722.37200000000007</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" s="22">
         <v>0</v>
@@ -2104,249 +2216,271 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="22">
-        <v>0</v>
+        <v>49</v>
+      </c>
+      <c r="B19" s="23">
+        <v>0.72826830937713893</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="21">
-        <v>0.1059451040642144</v>
+        <v>51</v>
+      </c>
+      <c r="B20" s="23">
+        <v>0.49555099247091028</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="23">
-        <v>7.50000701190464</v>
+        <v>53</v>
+      </c>
+      <c r="B21" s="22">
+        <v>0</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B22" s="22">
-        <v>12</v>
+        <v>55</v>
+      </c>
+      <c r="B22" s="21">
+        <v>0.1060021476832092</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="23">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="B23" s="24">
+        <v>10</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="19">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B24" s="22">
+        <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="23">
-        <v>99.275988191116866</v>
+        <v>61</v>
+      </c>
+      <c r="B25" s="24">
+        <v>1</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="19">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B27" s="19">
+        <v>64</v>
+      </c>
+      <c r="B27" s="24">
+        <v>105.82084532332119</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="19">
+        <v>0.15</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="19">
         <v>-0.1</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C29" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="F30" s="14" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="B32" s="14" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B31" s="24">
-        <v>7.2399995999999994E-2</v>
-      </c>
-      <c r="C31" s="24">
-        <v>6.0500002999999997E-2</v>
-      </c>
-      <c r="D31" s="24">
-        <v>5.0375002249999988E-2</v>
-      </c>
-      <c r="E31" s="24">
-        <v>4.02500015E-2</v>
-      </c>
-      <c r="F31" s="24">
-        <v>3.0125000749999999E-2</v>
-      </c>
-      <c r="G31" s="24">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="D32" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="24">
-        <v>0.12802127279350331</v>
-      </c>
-      <c r="C32" s="24">
-        <v>0.1331158836373742</v>
-      </c>
-      <c r="D32" s="24">
-        <v>0.13821049448124501</v>
-      </c>
-      <c r="E32" s="24">
-        <v>0.14330510532511581</v>
-      </c>
-      <c r="F32" s="24">
-        <v>0.1483997161689867</v>
-      </c>
-      <c r="G32" s="24">
-        <v>0.15349432701285751</v>
+      <c r="E32" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="24">
-        <v>3.4113082716595633E-2</v>
-      </c>
-      <c r="C33" s="24">
-        <v>3.4113082716595633E-2</v>
-      </c>
-      <c r="D33" s="24">
-        <v>3.4113082716595633E-2</v>
-      </c>
-      <c r="E33" s="24">
-        <v>3.4113082716595633E-2</v>
-      </c>
-      <c r="F33" s="24">
-        <v>3.4113082716595633E-2</v>
-      </c>
-      <c r="G33" s="24">
-        <v>3.4113082716595633E-2</v>
+        <v>75</v>
+      </c>
+      <c r="B33" s="25">
+        <v>7.5766726065204404E-2</v>
+      </c>
+      <c r="C33" s="25">
+        <v>6.0500002999999997E-2</v>
+      </c>
+      <c r="D33" s="25">
+        <v>5.0375002249999988E-2</v>
+      </c>
+      <c r="E33" s="25">
+        <v>4.02500015E-2</v>
+      </c>
+      <c r="F33" s="25">
+        <v>3.0125000749999999E-2</v>
+      </c>
+      <c r="G33" s="25">
+        <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="24">
-        <v>5.5799457283303433E-2</v>
-      </c>
-      <c r="C34" s="24">
-        <v>5.1803313197127818E-2</v>
-      </c>
-      <c r="D34" s="24">
-        <v>4.7807169110952223E-2</v>
-      </c>
-      <c r="E34" s="24">
-        <v>4.3811025024776622E-2</v>
-      </c>
-      <c r="F34" s="24">
-        <v>3.981488093860102E-2</v>
-      </c>
-      <c r="G34" s="24">
-        <v>3.5818736852425419E-2</v>
+        <v>76</v>
+      </c>
+      <c r="B34" s="25">
+        <v>0.1308433378727224</v>
+      </c>
+      <c r="C34" s="25">
+        <v>0.13537353570074939</v>
+      </c>
+      <c r="D34" s="25">
+        <v>0.1399037335287765</v>
+      </c>
+      <c r="E34" s="25">
+        <v>0.14443393135680349</v>
+      </c>
+      <c r="F34" s="25">
+        <v>0.14896412918483051</v>
+      </c>
+      <c r="G34" s="25">
+        <v>0.15349432701285751</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="24">
+        <v>77</v>
+      </c>
+      <c r="B35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+      <c r="C35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+      <c r="D35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+      <c r="E35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+      <c r="F35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+      <c r="G35" s="25">
+        <v>3.4113082716595633E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="25">
+        <v>5.5799457283303433E-2</v>
+      </c>
+      <c r="C36" s="25">
+        <v>5.1803313197127818E-2</v>
+      </c>
+      <c r="D36" s="25">
+        <v>4.7807169110952223E-2</v>
+      </c>
+      <c r="E36" s="25">
+        <v>4.3811025024776622E-2</v>
+      </c>
+      <c r="F36" s="25">
+        <v>3.981488093860102E-2</v>
+      </c>
+      <c r="G36" s="25">
+        <v>3.5818736852425419E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="E35" s="24">
+      <c r="E37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="F35" s="24">
+      <c r="F37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="G35" s="24">
+      <c r="G37" s="25">
         <v>3.8989408713458788E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>76</v>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A40" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2365,34 +2499,34 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B5" s="18">
         <v>3177.991</v>
@@ -2408,26 +2542,26 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26">
+      <c r="A6" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27">
         <f>IF(B5=0,"",C5/B5-1)</f>
         <v>7.4136144501353085E-2</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <f>IF(C5=0,"",D5/C5-1)</f>
         <v>0.10878531284466963</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f>IF(D5=0,"",E5/D5-1)</f>
         <v>4.2173675488990092E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B7" s="18">
         <v>713.84199999999998</v>
@@ -2444,7 +2578,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B8" s="18">
         <v>298.53032499999989</v>
@@ -2461,49 +2595,49 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="27">
+        <v>93</v>
+      </c>
+      <c r="B9" s="28">
         <f>B7-B8</f>
         <v>415.31167500000009</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <f>C7-C8</f>
         <v>545.9209800000001</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <f>D7-D8</f>
         <v>672.32259999999997</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <f>E7-E8</f>
         <v>484.89270000000005</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="26">
+      <c r="A10" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="27">
         <f>IF(B5=0,"",B9/B5)</f>
         <v>0.13068371653664221</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>IF(C5=0,"",C9/C5)</f>
         <v>0.15992552719347203</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>IF(D5=0,"",D9/D5)</f>
         <v>0.17763079189546793</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>IF(E5=0,"",E9/E5)</f>
         <v>0.12292666194963253</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B11" s="18">
         <v>348.29599999999999</v>
@@ -2520,7 +2654,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B12" s="18">
         <v>263.34999999999991</v>
@@ -2537,70 +2671,70 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="28">
+        <v>96</v>
+      </c>
+      <c r="B13" s="29">
         <f>MAX(B11-B12,0)</f>
         <v>84.946000000000083</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <f>MAX(C11-C12,0)</f>
         <v>107.88600000000014</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <f>MAX(D11-D12,0)</f>
         <v>131.12200000000007</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>MAX(E11-E12,0)</f>
         <v>142.3649999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="27">
+        <v>97</v>
+      </c>
+      <c r="B14" s="28">
         <f>B9-B13</f>
         <v>330.36567500000001</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>C9-C13</f>
         <v>438.03497999999996</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>D9-D13</f>
         <v>541.20059999999989</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>E9-E13</f>
         <v>342.52770000000015</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="26">
+      <c r="A15" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="27">
         <f>IF(B5=0,"",B14/B5)</f>
         <v>0.10395425128642592</v>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>IF(C5=0,"",C14/C5)</f>
         <v>0.12832072346016443</v>
       </c>
-      <c r="D15" s="26">
+      <c r="D15" s="27">
         <f>IF(D5=0,"",D14/D5)</f>
         <v>0.14298774301548448</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f>IF(E5=0,"",E14/E5)</f>
         <v>8.6835266413136686E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="25" t="s">
-        <v>94</v>
+      <c r="A16" s="26" t="s">
+        <v>99</v>
       </c>
       <c r="B16" s="19">
         <v>0.2184552478426651</v>
@@ -2617,28 +2751,28 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" s="27">
+        <v>100</v>
+      </c>
+      <c r="B17" s="28">
         <f>B14*(1-B16)</f>
         <v>258.19555958916567</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C14*(1-C16)</f>
         <v>341.50966806895417</v>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D14*(1-D16)</f>
         <v>433.03848518134129</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="28">
         <f>E14*(1-E16)</f>
         <v>272.78560048357025</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B18" s="18">
         <v>-119.264</v>
@@ -2655,7 +2789,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B19" s="18">
         <v>-61.558</v>
@@ -2672,49 +2806,49 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="27">
+        <v>103</v>
+      </c>
+      <c r="B20" s="28">
         <f>B17+B13+B18+B19</f>
         <v>162.31955958916575</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="28">
         <f>C17+C13+C18+C19</f>
         <v>441.58066806895431</v>
       </c>
-      <c r="D20" s="27">
+      <c r="D20" s="28">
         <f>D17+D13+D18+D19</f>
         <v>358.35448518134126</v>
       </c>
-      <c r="E20" s="27">
+      <c r="E20" s="28">
         <f>E17+E13+E18+E19</f>
         <v>13.376600483570144</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="26">
+      <c r="A21" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="27">
         <f>IF(B5=0,"",B20/B5)</f>
         <v>5.1076154586078358E-2</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>IF(C5=0,"",C20/C5)</f>
         <v>0.12935941963500483</v>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="27">
         <f>IF(D5=0,"",D20/D5)</f>
         <v>9.4678939815580163E-2</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f>IF(E5=0,"",E20/E5)</f>
         <v>3.3911437430984587E-3</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B22" s="18">
         <v>249.244</v>
@@ -2731,24 +2865,24 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="23">
+        <v>106</v>
+      </c>
+      <c r="B23" s="24">
         <v>6.13</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="24">
         <v>7.72</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="24">
         <v>9.81</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>5.64</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B24" s="18">
         <v>75.978999999999999</v>
@@ -2765,7 +2899,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B25" s="18">
         <v>1333.431</v>
@@ -2782,7 +2916,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B26" s="18">
         <v>781.78499999999997</v>
@@ -2799,7 +2933,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B27" s="18">
         <v>475.66699999999997</v>
@@ -2816,28 +2950,28 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B28" s="29">
+        <v>111</v>
+      </c>
+      <c r="B28" s="30">
         <f>IF(B9&lt;=0,"n.m.",B27/B9)</f>
         <v>1.1453253752136872</v>
       </c>
-      <c r="C28" s="29">
+      <c r="C28" s="30">
         <f>IF(C9&lt;=0,"n.m.",C27/C9)</f>
         <v>0.54282214982835053</v>
       </c>
-      <c r="D28" s="29">
+      <c r="D28" s="30">
         <f>IF(D9&lt;=0,"n.m.",D27/D9)</f>
         <v>0.3913805664126121</v>
       </c>
-      <c r="E28" s="29">
+      <c r="E28" s="30">
         <f>IF(E9&lt;=0,"n.m.",E27/E9)</f>
         <v>1.4897563935278875</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B29" s="18">
         <v>11.453675</v>
@@ -2868,603 +3002,603 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="C5" s="30">
-        <f>Inputs!B31</f>
-        <v>7.2399995999999994E-2</v>
-      </c>
-      <c r="D5" s="30">
-        <f>Inputs!C31</f>
+        <v>75</v>
+      </c>
+      <c r="C5" s="31">
+        <f>Inputs!B33</f>
+        <v>7.5766726065204404E-2</v>
+      </c>
+      <c r="D5" s="31">
+        <f>Inputs!C33</f>
         <v>6.0500002999999997E-2</v>
       </c>
-      <c r="E5" s="30">
-        <f>Inputs!D31</f>
+      <c r="E5" s="31">
+        <f>Inputs!D33</f>
         <v>5.0375002249999988E-2</v>
       </c>
-      <c r="F5" s="30">
-        <f>Inputs!E31</f>
+      <c r="F5" s="31">
+        <f>Inputs!E33</f>
         <v>4.02500015E-2</v>
       </c>
-      <c r="G5" s="30">
-        <f>Inputs!F31</f>
+      <c r="G5" s="31">
+        <f>Inputs!F33</f>
         <v>3.0125000749999999E-2</v>
       </c>
-      <c r="H5" s="30">
-        <f>Inputs!G31</f>
+      <c r="H5" s="31">
+        <f>Inputs!G33</f>
         <v>0.02</v>
       </c>
-      <c r="I5" s="30">
+      <c r="I5" s="31">
         <f>Inputs!$B$11</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="31">
+        <v>89</v>
+      </c>
+      <c r="B6" s="32">
         <f>Historicals!E5</f>
         <v>3944.569</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <f t="shared" ref="C6:I6" si="0">B6*(1+C5)</f>
-        <v>4230.1557798217236</v>
-      </c>
-      <c r="D6" s="27">
+        <v>4243.436078868297</v>
+      </c>
+      <c r="D6" s="28">
         <f t="shared" si="0"/>
-        <v>4486.0802171914056</v>
-      </c>
-      <c r="E6" s="27">
+        <v>4500.1639743701371</v>
+      </c>
+      <c r="E6" s="28">
         <f t="shared" si="0"/>
-        <v>4712.0665182261037</v>
-      </c>
-      <c r="F6" s="27">
+        <v>4726.8597447044021</v>
+      </c>
+      <c r="F6" s="28">
         <f t="shared" si="0"/>
-        <v>4901.7272026528044</v>
-      </c>
-      <c r="G6" s="27">
+        <v>4917.1158565190444</v>
+      </c>
+      <c r="G6" s="28">
         <f t="shared" si="0"/>
-        <v>5049.3917383090156</v>
-      </c>
-      <c r="H6" s="27">
+        <v>5065.2439753845174</v>
+      </c>
+      <c r="H6" s="28">
         <f t="shared" si="0"/>
-        <v>5150.3795730751963</v>
-      </c>
-      <c r="I6" s="27">
+        <v>5166.5488548922076</v>
+      </c>
+      <c r="I6" s="28">
         <f t="shared" si="0"/>
-        <v>5253.3871645366999</v>
+        <v>5269.8798319900516</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="27">
         <f>B8/B6</f>
         <v>0.12292666194963253</v>
       </c>
-      <c r="C7" s="30">
-        <f>Inputs!B32</f>
-        <v>0.12802127279350331</v>
-      </c>
-      <c r="D7" s="30">
-        <f>Inputs!C32</f>
-        <v>0.1331158836373742</v>
-      </c>
-      <c r="E7" s="30">
-        <f>Inputs!D32</f>
-        <v>0.13821049448124501</v>
-      </c>
-      <c r="F7" s="30">
-        <f>Inputs!E32</f>
-        <v>0.14330510532511581</v>
-      </c>
-      <c r="G7" s="30">
-        <f>Inputs!F32</f>
-        <v>0.1483997161689867</v>
-      </c>
-      <c r="H7" s="30">
-        <f>Inputs!G32</f>
+      <c r="C7" s="31">
+        <f>Inputs!B34</f>
+        <v>0.1308433378727224</v>
+      </c>
+      <c r="D7" s="31">
+        <f>Inputs!C34</f>
+        <v>0.13537353570074939</v>
+      </c>
+      <c r="E7" s="31">
+        <f>Inputs!D34</f>
+        <v>0.1399037335287765</v>
+      </c>
+      <c r="F7" s="31">
+        <f>Inputs!E34</f>
+        <v>0.14443393135680349</v>
+      </c>
+      <c r="G7" s="31">
+        <f>Inputs!F34</f>
+        <v>0.14896412918483051</v>
+      </c>
+      <c r="H7" s="31">
+        <f>Inputs!G34</f>
         <v>0.15349432701285751</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="27">
         <f>H7</f>
         <v>0.15349432701285751</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B8" s="31">
+        <v>93</v>
+      </c>
+      <c r="B8" s="32">
         <f>Historicals!E9</f>
         <v>484.89270000000005</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <f t="shared" ref="C8:I8" si="1">C6*C7</f>
-        <v>541.5499270475716</v>
-      </c>
-      <c r="D8" s="27">
+        <v>555.22534060866485</v>
+      </c>
+      <c r="D8" s="28">
         <f t="shared" si="1"/>
-        <v>597.16853217957748</v>
-      </c>
-      <c r="E8" s="27">
+        <v>609.203108443622</v>
+      </c>
+      <c r="E8" s="28">
         <f t="shared" si="1"/>
-        <v>651.25704351254831</v>
-      </c>
-      <c r="F8" s="27">
+        <v>661.30532615102516</v>
+      </c>
+      <c r="F8" s="28">
         <f t="shared" si="1"/>
-        <v>702.44253305114546</v>
-      </c>
-      <c r="G8" s="27">
+        <v>710.19837409392164</v>
+      </c>
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
-        <v>749.3283007910843</v>
-      </c>
-      <c r="H8" s="27">
+        <v>754.53965790186373</v>
+      </c>
+      <c r="H8" s="28">
         <f t="shared" si="1"/>
-        <v>790.55404642994563</v>
-      </c>
-      <c r="I8" s="27">
+        <v>793.03593946072897</v>
+      </c>
+      <c r="I8" s="28">
         <f t="shared" si="1"/>
-        <v>806.36512735854444</v>
+        <v>808.89665824994358</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" s="30">
-        <f>Inputs!B33</f>
+      <c r="A9" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="31">
+        <f>Inputs!B35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="D9" s="30">
-        <f>Inputs!C33</f>
+      <c r="D9" s="31">
+        <f>Inputs!C35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="E9" s="30">
-        <f>Inputs!D33</f>
+      <c r="E9" s="31">
+        <f>Inputs!D35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="F9" s="30">
-        <f>Inputs!E33</f>
+      <c r="F9" s="31">
+        <f>Inputs!E35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="G9" s="30">
-        <f>Inputs!F33</f>
+      <c r="G9" s="31">
+        <f>Inputs!F35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="H9" s="30">
-        <f>Inputs!G33</f>
+      <c r="H9" s="31">
+        <f>Inputs!G35</f>
         <v>3.4113082716595633E-2</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="27">
         <f>H9</f>
         <v>3.4113082716595633E-2</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B10" s="31">
+        <v>96</v>
+      </c>
+      <c r="B10" s="32">
         <f>Historicals!E13</f>
         <v>142.3649999999999</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f t="shared" ref="C10:I10" si="2">C6*C9</f>
-        <v>144.30365402114356</v>
-      </c>
-      <c r="D10" s="28">
+        <v>144.75668596102045</v>
+      </c>
+      <c r="D10" s="29">
         <f t="shared" si="2"/>
-        <v>153.03402552233374</v>
-      </c>
-      <c r="E10" s="28">
+        <v>153.51446589593223</v>
+      </c>
+      <c r="E10" s="29">
         <f t="shared" si="2"/>
-        <v>160.74311490234786</v>
-      </c>
-      <c r="F10" s="28">
+        <v>161.2477574608474</v>
+      </c>
+      <c r="F10" s="29">
         <f t="shared" si="2"/>
-        <v>167.21302551828205</v>
-      </c>
-      <c r="G10" s="28">
+        <v>167.73797994051816</v>
+      </c>
+      <c r="G10" s="29">
         <f t="shared" si="2"/>
-        <v>172.25031803743005</v>
-      </c>
-      <c r="H10" s="28">
+        <v>172.79108671202974</v>
+      </c>
+      <c r="H10" s="29">
         <f t="shared" si="2"/>
-        <v>175.69532439817868</v>
-      </c>
-      <c r="I10" s="28">
+        <v>176.24690844627034</v>
+      </c>
+      <c r="I10" s="29">
         <f t="shared" si="2"/>
-        <v>179.20923088614222</v>
+        <v>179.77184661519573</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B11" s="31">
+        <v>97</v>
+      </c>
+      <c r="B11" s="32">
         <f>Historicals!E14</f>
         <v>342.52770000000015</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <f t="shared" ref="C11:I11" si="3">C8-C10</f>
-        <v>397.24627302642807</v>
-      </c>
-      <c r="D11" s="27">
+        <v>410.46865464764437</v>
+      </c>
+      <c r="D11" s="28">
         <f t="shared" si="3"/>
-        <v>444.13450665724372</v>
-      </c>
-      <c r="E11" s="27">
+        <v>455.68864254768977</v>
+      </c>
+      <c r="E11" s="28">
         <f t="shared" si="3"/>
-        <v>490.51392861020042</v>
-      </c>
-      <c r="F11" s="27">
+        <v>500.05756869017773</v>
+      </c>
+      <c r="F11" s="28">
         <f t="shared" si="3"/>
-        <v>535.22950753286341</v>
-      </c>
-      <c r="G11" s="27">
+        <v>542.46039415340351</v>
+      </c>
+      <c r="G11" s="28">
         <f t="shared" si="3"/>
-        <v>577.07798275365428</v>
-      </c>
-      <c r="H11" s="27">
+        <v>581.74857118983402</v>
+      </c>
+      <c r="H11" s="28">
         <f t="shared" si="3"/>
-        <v>614.858722031767</v>
-      </c>
-      <c r="I11" s="27">
+        <v>616.7890310144586</v>
+      </c>
+      <c r="I11" s="28">
         <f t="shared" si="3"/>
-        <v>627.15589647240222</v>
+        <v>629.12481163474786</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="26">
+      <c r="A12" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="27">
         <f t="shared" ref="C12:I12" si="4">C11/C6</f>
-        <v>9.3908190076907677E-2</v>
-      </c>
-      <c r="D12" s="26">
+        <v>9.6730255156126752E-2</v>
+      </c>
+      <c r="D12" s="27">
         <f t="shared" si="4"/>
-        <v>9.9002800920778553E-2</v>
-      </c>
-      <c r="E12" s="26">
+        <v>0.10126045298415376</v>
+      </c>
+      <c r="E12" s="27">
         <f t="shared" si="4"/>
-        <v>0.10409741176464937</v>
-      </c>
-      <c r="F12" s="26">
+        <v>0.10579065081218085</v>
+      </c>
+      <c r="F12" s="27">
         <f t="shared" si="4"/>
-        <v>0.10919202260852018</v>
-      </c>
-      <c r="G12" s="26">
+        <v>0.11032084864020786</v>
+      </c>
+      <c r="G12" s="27">
         <f t="shared" si="4"/>
-        <v>0.11428663345239108</v>
-      </c>
-      <c r="H12" s="26">
+        <v>0.11485104646823489</v>
+      </c>
+      <c r="H12" s="27">
         <f t="shared" si="4"/>
-        <v>0.11938124429626189</v>
-      </c>
-      <c r="I12" s="26">
+        <v>0.11938124429626186</v>
+      </c>
+      <c r="I12" s="27">
         <f t="shared" si="4"/>
         <v>0.11938124429626187</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C13" s="28">
+        <v>116</v>
+      </c>
+      <c r="C13" s="29">
         <f>-MAX(C11,0)*Inputs!$B$10</f>
-        <v>-87.394180065814183</v>
-      </c>
-      <c r="D13" s="28">
+        <v>-90.303104022481762</v>
+      </c>
+      <c r="D13" s="29">
         <f>-MAX(D11,0)*Inputs!$B$10</f>
-        <v>-97.709591464593615</v>
-      </c>
-      <c r="E13" s="28">
+        <v>-100.25150136049174</v>
+      </c>
+      <c r="E13" s="29">
         <f>-MAX(E11,0)*Inputs!$B$10</f>
-        <v>-107.91306429424409</v>
-      </c>
-      <c r="F13" s="28">
+        <v>-110.0126651118391</v>
+      </c>
+      <c r="F13" s="29">
         <f>-MAX(F11,0)*Inputs!$B$10</f>
-        <v>-117.75049165722994</v>
-      </c>
-      <c r="G13" s="28">
+        <v>-119.34128671374877</v>
+      </c>
+      <c r="G13" s="29">
         <f>-MAX(G11,0)*Inputs!$B$10</f>
-        <v>-126.95715620580394</v>
-      </c>
-      <c r="H13" s="28">
+        <v>-127.98468566176349</v>
+      </c>
+      <c r="H13" s="29">
         <f>-MAX(H11,0)*Inputs!$B$10</f>
-        <v>-135.26891884698875</v>
-      </c>
-      <c r="I13" s="28">
+        <v>-135.69358682318088</v>
+      </c>
+      <c r="I13" s="29">
         <f>-MAX(I11,0)*Inputs!$B$10</f>
-        <v>-137.97429722392849</v>
+        <v>-138.40745855964454</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B14" s="31">
+        <v>100</v>
+      </c>
+      <c r="B14" s="32">
         <f>Historicals!E17</f>
         <v>272.78560048357025</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f t="shared" ref="C14:I14" si="5">C11+C13</f>
-        <v>309.8520929606139</v>
-      </c>
-      <c r="D14" s="27">
+        <v>320.16555062516261</v>
+      </c>
+      <c r="D14" s="28">
         <f t="shared" si="5"/>
-        <v>346.42491519265013</v>
-      </c>
-      <c r="E14" s="27">
+        <v>355.43714118719799</v>
+      </c>
+      <c r="E14" s="28">
         <f t="shared" si="5"/>
-        <v>382.6008643159563</v>
-      </c>
-      <c r="F14" s="27">
+        <v>390.04490357833862</v>
+      </c>
+      <c r="F14" s="28">
         <f t="shared" si="5"/>
-        <v>417.47901587563348</v>
-      </c>
-      <c r="G14" s="27">
+        <v>423.11910743965473</v>
+      </c>
+      <c r="G14" s="28">
         <f t="shared" si="5"/>
-        <v>450.12082654785036</v>
-      </c>
-      <c r="H14" s="27">
+        <v>453.76388552807055</v>
+      </c>
+      <c r="H14" s="28">
         <f t="shared" si="5"/>
-        <v>479.58980318477825</v>
-      </c>
-      <c r="I14" s="27">
+        <v>481.09544419127769</v>
+      </c>
+      <c r="I14" s="28">
         <f t="shared" si="5"/>
-        <v>489.18159924847373</v>
+        <v>490.71735307510335</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" s="30">
-        <f>Inputs!B34</f>
+      <c r="A15" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="31">
+        <f>Inputs!B36</f>
         <v>5.5799457283303433E-2</v>
       </c>
-      <c r="D15" s="30">
-        <f>Inputs!C34</f>
+      <c r="D15" s="31">
+        <f>Inputs!C36</f>
         <v>5.1803313197127818E-2</v>
       </c>
-      <c r="E15" s="30">
-        <f>Inputs!D34</f>
+      <c r="E15" s="31">
+        <f>Inputs!D36</f>
         <v>4.7807169110952223E-2</v>
       </c>
-      <c r="F15" s="30">
-        <f>Inputs!E34</f>
+      <c r="F15" s="31">
+        <f>Inputs!E36</f>
         <v>4.3811025024776622E-2</v>
       </c>
-      <c r="G15" s="30">
-        <f>Inputs!F34</f>
+      <c r="G15" s="31">
+        <f>Inputs!F36</f>
         <v>3.981488093860102E-2</v>
       </c>
-      <c r="H15" s="30">
-        <f>Inputs!G34</f>
+      <c r="H15" s="31">
+        <f>Inputs!G36</f>
         <v>3.5818736852425419E-2</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <f>H15</f>
         <v>3.5818736852425419E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="31">
+        <v>101</v>
+      </c>
+      <c r="B16" s="32">
         <f>Historicals!E18</f>
         <v>-254.04300000000001</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f t="shared" ref="C16:I16" si="6">-C6*C15</f>
-        <v>-236.04039673788139</v>
-      </c>
-      <c r="D16" s="28">
+        <v>-236.78143021724017</v>
+      </c>
+      <c r="D16" s="29">
         <f t="shared" si="6"/>
-        <v>-232.39381851860557</v>
-      </c>
-      <c r="E16" s="28">
+        <v>-233.12340380272769</v>
+      </c>
+      <c r="E16" s="29">
         <f t="shared" si="6"/>
-        <v>-225.27056089889118</v>
-      </c>
-      <c r="F16" s="28">
+        <v>-225.97778317883581</v>
+      </c>
+      <c r="F16" s="29">
         <f t="shared" si="6"/>
-        <v>-214.74969314005031</v>
-      </c>
-      <c r="G16" s="28">
+        <v>-215.42388583968179</v>
+      </c>
+      <c r="G16" s="29">
         <f t="shared" si="6"/>
-        <v>-201.0409308731291</v>
-      </c>
-      <c r="H16" s="28">
+        <v>-201.67208580490069</v>
+      </c>
+      <c r="H16" s="29">
         <f t="shared" si="6"/>
-        <v>-184.48009061808762</v>
-      </c>
-      <c r="I16" s="28">
+        <v>-185.05925386858385</v>
+      </c>
+      <c r="I16" s="29">
         <f t="shared" si="6"/>
-        <v>-188.16969243044937</v>
+        <v>-188.76043894595554</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="30">
-        <f>Inputs!B35</f>
+      <c r="A17" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="31">
+        <f>Inputs!B37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="D17" s="30">
-        <f>Inputs!C35</f>
+      <c r="D17" s="31">
+        <f>Inputs!C37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="E17" s="30">
-        <f>Inputs!D35</f>
+      <c r="E17" s="31">
+        <f>Inputs!D37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="F17" s="30">
-        <f>Inputs!E35</f>
+      <c r="F17" s="31">
+        <f>Inputs!E37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="G17" s="30">
-        <f>Inputs!F35</f>
+      <c r="G17" s="31">
+        <f>Inputs!F37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="H17" s="30">
-        <f>Inputs!G35</f>
+      <c r="H17" s="31">
+        <f>Inputs!G37</f>
         <v>3.8989408713458788E-2</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>H17</f>
         <v>3.8989408713458788E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="B18" s="31">
+        <v>102</v>
+      </c>
+      <c r="B18" s="32">
         <f>Historicals!E19</f>
         <v>-147.73099999999999</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f t="shared" ref="C18:I18" si="7">-C17*(C6-B6)</f>
-        <v>-11.134859681629749</v>
-      </c>
-      <c r="D18" s="28">
+        <v>-11.652650688993557</v>
+      </c>
+      <c r="D18" s="29">
         <f t="shared" si="7"/>
-        <v>-9.9783424883685168</v>
-      </c>
-      <c r="E18" s="28">
+        <v>-10.009668845867381</v>
+      </c>
+      <c r="E18" s="29">
         <f t="shared" si="7"/>
-        <v>-8.8110722546845768</v>
-      </c>
-      <c r="F18" s="28">
+        <v>-8.8387340431750463</v>
+      </c>
+      <c r="F18" s="29">
         <f t="shared" si="7"/>
-        <v>-7.3947579419869642</v>
-      </c>
-      <c r="G18" s="28">
+        <v>-7.4179733037746036</v>
+      </c>
+      <c r="G18" s="29">
         <f t="shared" si="7"/>
-        <v>-5.7573529331831281</v>
-      </c>
-      <c r="H18" s="28">
+        <v>-5.7754277684017312</v>
+      </c>
+      <c r="H18" s="29">
         <f t="shared" si="7"/>
-        <v>-3.93745596478586</v>
-      </c>
-      <c r="I18" s="28">
+        <v>-3.9498173517930288</v>
+      </c>
+      <c r="I18" s="29">
         <f t="shared" si="7"/>
-        <v>-4.0162050840815509</v>
+        <v>-4.0288136988288885</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B19" s="31">
+        <v>103</v>
+      </c>
+      <c r="B19" s="32">
         <f>Historicals!E20</f>
         <v>13.376600483570144</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="28">
         <f t="shared" ref="C19:I19" si="8">C14+C10+C16+C18</f>
-        <v>206.98049056224636</v>
-      </c>
-      <c r="D19" s="27">
+        <v>216.48815567994936</v>
+      </c>
+      <c r="D19" s="28">
         <f t="shared" si="8"/>
-        <v>257.08677970800977</v>
-      </c>
-      <c r="E19" s="27">
+        <v>265.81853443453514</v>
+      </c>
+      <c r="E19" s="28">
         <f t="shared" si="8"/>
-        <v>309.26234606472843</v>
-      </c>
-      <c r="F19" s="27">
+        <v>316.47614381717511</v>
+      </c>
+      <c r="F19" s="28">
         <f t="shared" si="8"/>
-        <v>362.54759031187831</v>
-      </c>
-      <c r="G19" s="27">
+        <v>368.01522823671644</v>
+      </c>
+      <c r="G19" s="28">
         <f t="shared" si="8"/>
-        <v>415.57286077896811</v>
-      </c>
-      <c r="H19" s="27">
+        <v>419.10745866679781</v>
+      </c>
+      <c r="H19" s="28">
         <f t="shared" si="8"/>
-        <v>466.86758100008342</v>
-      </c>
-      <c r="I19" s="27">
+        <v>468.33328141717124</v>
+      </c>
+      <c r="I19" s="28">
         <f t="shared" si="8"/>
-        <v>476.20493262008506</v>
+        <v>477.69994704551459</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="26">
+      <c r="A20" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="27">
         <f t="shared" ref="C20:I20" si="9">C19/C6</f>
-        <v>4.8929756097769381E-2</v>
-      </c>
-      <c r="D20" s="26">
+        <v>5.1017183163905619E-2</v>
+      </c>
+      <c r="D20" s="27">
         <f t="shared" si="9"/>
-        <v>5.7307664433375594E-2</v>
-      </c>
-      <c r="E20" s="26">
+        <v>5.9068633042808238E-2</v>
+      </c>
+      <c r="E20" s="27">
         <f t="shared" si="9"/>
-        <v>6.5631999223379547E-2</v>
-      </c>
-      <c r="F20" s="26">
+        <v>6.69527256804541E-2</v>
+      </c>
+      <c r="F20" s="27">
         <f t="shared" si="9"/>
-        <v>7.3963232820396102E-2</v>
-      </c>
-      <c r="G20" s="26">
+        <v>7.4843717125112466E-2</v>
+      </c>
+      <c r="G20" s="27">
         <f t="shared" si="9"/>
-        <v>8.2301568647581064E-2</v>
-      </c>
-      <c r="H20" s="26">
+        <v>8.2741810799939239E-2</v>
+      </c>
+      <c r="H20" s="27">
         <f t="shared" si="9"/>
         <v>9.0647218205186661E-2</v>
       </c>
-      <c r="I20" s="26">
+      <c r="I20" s="27">
         <f t="shared" si="9"/>
         <v>9.0647218205186661E-2</v>
       </c>
@@ -3476,7 +3610,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3486,17 +3620,17 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>24</v>
@@ -3543,9 +3677,9 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" s="32">
+        <v>120</v>
+      </c>
+      <c r="B9" s="33">
         <f>B5+B6*B7+B8</f>
         <v>8.8293499999999997E-2</v>
       </c>
@@ -3570,56 +3704,93 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="33">
+        <v>121</v>
+      </c>
+      <c r="B12" s="34">
         <f>B10*(1-B11)</f>
         <v>7.024741524167244E-2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="28">
+        <v>122</v>
+      </c>
+      <c r="B13" s="29">
         <f>(Inputs!$B$5*Inputs!$B$6)*Inputs!$B$7</f>
-        <v>4828.6452455999997</v>
+        <v>4966.8387964000003</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" s="31">
+        <v>123</v>
+      </c>
+      <c r="B14" s="32">
         <f>Inputs!$B$17</f>
         <v>722.37200000000007</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="34">
+        <v>124</v>
+      </c>
+      <c r="B15" s="35">
         <f>B13/(B13+B14)</f>
-        <v>0.86986673468316345</v>
+        <v>0.87302773163949199</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="34">
+        <v>125</v>
+      </c>
+      <c r="B16" s="35">
         <f>B14/(B13+B14)</f>
-        <v>0.13013326531683655</v>
+        <v>0.12697226836050796</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="33">
         <f>B15*B9+B16*B12</f>
-        <v>8.5945104064214434E-2</v>
+        <v>8.6002147683209157E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B20" s="24">
+        <v>0.82416121800533415</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B21" s="24">
+        <v>0.91765605228251701</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" s="24">
+        <v>0.94482955502928645</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="22">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3638,160 +3809,160 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="35">
+        <v>103</v>
+      </c>
+      <c r="B5" s="36">
         <f>Forecast!C19</f>
-        <v>206.98049056224636</v>
-      </c>
-      <c r="C5" s="35">
+        <v>216.48815567994936</v>
+      </c>
+      <c r="C5" s="36">
         <f>Forecast!D19</f>
-        <v>257.08677970800977</v>
-      </c>
-      <c r="D5" s="35">
+        <v>265.81853443453514</v>
+      </c>
+      <c r="D5" s="36">
         <f>Forecast!E19</f>
-        <v>309.26234606472843</v>
-      </c>
-      <c r="E5" s="35">
+        <v>316.47614381717511</v>
+      </c>
+      <c r="E5" s="36">
         <f>Forecast!F19</f>
-        <v>362.54759031187831</v>
-      </c>
-      <c r="F5" s="35">
+        <v>368.01522823671644</v>
+      </c>
+      <c r="F5" s="36">
         <f>Forecast!G19</f>
-        <v>415.57286077896811</v>
-      </c>
-      <c r="G5" s="35">
+        <v>419.10745866679781</v>
+      </c>
+      <c r="G5" s="36">
         <f>Forecast!H19</f>
-        <v>466.86758100008342</v>
+        <v>468.33328141717124</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B6" s="36">
-        <f>1-0.5*Inputs!$B$18</f>
-        <v>1</v>
-      </c>
-      <c r="C6" s="36">
-        <f>2-0.5*Inputs!$B$18</f>
-        <v>2</v>
-      </c>
-      <c r="D6" s="36">
-        <f>3-0.5*Inputs!$B$18</f>
-        <v>3</v>
-      </c>
-      <c r="E6" s="36">
-        <f>4-0.5*Inputs!$B$18</f>
-        <v>4</v>
-      </c>
-      <c r="F6" s="36">
-        <f>5-0.5*Inputs!$B$18</f>
-        <v>5</v>
-      </c>
-      <c r="G6" s="36">
-        <f>6-0.5*Inputs!$B$18</f>
-        <v>6</v>
+        <v>134</v>
+      </c>
+      <c r="B6" s="37">
+        <f>IF(Inputs!$B$18=1,(1+Inputs!$B$20)/2,1)-Inputs!$B$19</f>
+        <v>0.27173169062286107</v>
+      </c>
+      <c r="C6" s="37">
+        <f>2-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>1.2717316906228611</v>
+      </c>
+      <c r="D6" s="37">
+        <f>3-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>2.2717316906228611</v>
+      </c>
+      <c r="E6" s="37">
+        <f>4-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>3.2717316906228611</v>
+      </c>
+      <c r="F6" s="37">
+        <f>5-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>4.2717316906228611</v>
+      </c>
+      <c r="G6" s="37">
+        <f>6-Inputs!$B$19-0.5*Inputs!$B$18</f>
+        <v>5.2717316906228611</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B7" s="37">
         <f>1/(1+WACC!$B$17)^B6</f>
-        <v>0.9208568612330772</v>
+        <v>0.97783069857086313</v>
       </c>
       <c r="C7" s="37">
         <f>1/(1+WACC!$B$17)^C6</f>
-        <v>0.84797735888003478</v>
+        <v>0.90039481105713259</v>
       </c>
       <c r="D7" s="37">
         <f>1/(1+WACC!$B$17)^D6</f>
-        <v>0.78086576909498362</v>
+        <v>0.82909118824300976</v>
       </c>
       <c r="E7" s="37">
         <f>1/(1+WACC!$B$17)^E6</f>
-        <v>0.71906560117315943</v>
+        <v>0.76343420683994712</v>
       </c>
       <c r="F7" s="37">
         <f>1/(1+WACC!$B$17)^F6</f>
-        <v>0.66215649251699127</v>
+        <v>0.70297670079989905</v>
       </c>
       <c r="G7" s="37">
         <f>1/(1+WACC!$B$17)^G6</f>
-        <v>0.6097513493443002</v>
+        <v>0.64730691582845745</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="27">
-        <f t="shared" ref="B8:G8" si="0">B5*B7</f>
-        <v>190.59940487563273</v>
-      </c>
-      <c r="C8" s="27">
-        <f t="shared" si="0"/>
-        <v>218.00376845977144</v>
-      </c>
-      <c r="D8" s="27">
-        <f t="shared" si="0"/>
-        <v>241.49237971195316</v>
-      </c>
-      <c r="E8" s="27">
-        <f t="shared" si="0"/>
-        <v>260.69550098149108</v>
-      </c>
-      <c r="F8" s="27">
-        <f t="shared" si="0"/>
-        <v>275.17426787865344</v>
-      </c>
-      <c r="G8" s="27">
-        <f t="shared" si="0"/>
-        <v>284.67313747991022</v>
+        <v>136</v>
+      </c>
+      <c r="B8" s="28">
+        <f>B5*(1-Inputs!$B$20)*B7</f>
+        <v>106.78618715750927</v>
+      </c>
+      <c r="C8" s="28">
+        <f>C5*C7</f>
+        <v>239.34162908766717</v>
+      </c>
+      <c r="D8" s="28">
+        <f>D5*D7</f>
+        <v>262.38758212794738</v>
+      </c>
+      <c r="E8" s="28">
+        <f>E5*E7</f>
+        <v>280.95541387391972</v>
+      </c>
+      <c r="F8" s="28">
+        <f>F5*F7</f>
+        <v>294.6227785742156</v>
+      </c>
+      <c r="G8" s="28">
+        <f>G5*G7</f>
+        <v>303.15537197397015</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="27">
+        <v>137</v>
+      </c>
+      <c r="B10" s="28">
         <f>SUM(B8:G8)</f>
-        <v>1470.6384593874118</v>
+        <v>1487.2489627952293</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -3809,70 +3980,70 @@
       </c>
       <c r="B12" s="7">
         <f>WACC!$B$17</f>
-        <v>8.5945104064214434E-2</v>
+        <v>8.6002147683209157E-2</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B13" s="28">
-        <f>IF(Inputs!$B$19=1,Forecast!$H$14*(1+B11)*(1-B11/Inputs!$B$20),$G$5*(1+B11))</f>
-        <v>476.20493262008512</v>
+        <v>138</v>
+      </c>
+      <c r="B13" s="29">
+        <f>IF(Inputs!$B$21=1,Forecast!$H$14*(1+B11)*(1-B11/Inputs!$B$22),$G$5*(1+B11))</f>
+        <v>477.69994704551465</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="27">
+        <v>139</v>
+      </c>
+      <c r="B14" s="28">
         <f>B13/(B12-B11)</f>
-        <v>7221.2325596814253</v>
+        <v>7237.6424679138254</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B15" s="27">
-        <f>B14/(1+B12)^6</f>
-        <v>4403.1562971947442</v>
+        <v>140</v>
+      </c>
+      <c r="B15" s="28">
+        <f>B14/(1+B12)^(6-Inputs!$B$19)</f>
+        <v>4684.9760237743631</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="B16" s="27">
+        <v>141</v>
+      </c>
+      <c r="B16" s="28">
         <f>B10+B15</f>
-        <v>5873.794756582156</v>
+        <v>6172.2249865695921</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="31">
+        <v>142</v>
+      </c>
+      <c r="B17" s="32">
         <f>-Inputs!$B$8</f>
-        <v>-722.37199999999996</v>
+        <v>-1081.2090000000001</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="B18" s="31">
+        <v>143</v>
+      </c>
+      <c r="B18" s="32">
         <f>-Inputs!$B$9</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B19" s="27">
+        <v>144</v>
+      </c>
+      <c r="B19" s="28">
         <f>B16+B17+B18</f>
-        <v>5151.4227565821557</v>
+        <v>5091.0159865695923</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -3886,61 +4057,61 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="B21" s="39">
         <f>B19/B20/Inputs!$B$6</f>
-        <v>126.74135132201357</v>
+        <v>125.25515303813016</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B22" s="4">
         <f>Inputs!$B$5</f>
-        <v>118.8</v>
+        <v>122.2</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B23" s="40">
         <f>B21/B22-1</f>
-        <v>6.6846391599440835E-2</v>
+        <v>2.5001252357857329E-2</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B24" s="34">
+        <v>148</v>
+      </c>
+      <c r="B24" s="35">
         <f>B15/B16</f>
-        <v>0.74962719667053079</v>
+        <v>0.75904168010216777</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="B25" s="29">
+        <v>149</v>
+      </c>
+      <c r="B25" s="30">
         <f>B14/Forecast!H8</f>
-        <v>9.1343945329123422</v>
+        <v>9.1264999576633095</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B26" s="4">
-        <f>Inputs!$B$24*B21+(1-Inputs!$B$24)*Inputs!$B$25</f>
-        <v>126.74135132201357</v>
+        <f>Inputs!$B$26*B21+(1-Inputs!$B$26)*Inputs!$B$27</f>
+        <v>125.25515303813016</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B27" s="7">
         <f>WACC!$B$9</f>
@@ -3949,20 +4120,20 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B28" s="41">
-        <f>IF(Inputs!$B$22&gt;0,Inputs!$B$21,0)</f>
-        <v>7.50000701190464</v>
+        <f>IF(Inputs!$B$24&gt;0,Inputs!$B$23,0)</f>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B29" s="41">
-        <f>IF(B26&lt;=0,0,B26*(1+B27)^(Inputs!$B$22/12)-B28)</f>
-        <v>130.43178181305913</v>
+        <f>IF(B26&lt;=0,0,B26*(1+B27)^(Inputs!$B$24/12)-B28)</f>
+        <v>126.31436889290231</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
@@ -3970,8 +4141,8 @@
         <v>5</v>
       </c>
       <c r="B30" s="39">
-        <f>IF(Inputs!$B$23&gt;0,MROUND(B29,Inputs!$B$23),B29)</f>
-        <v>130</v>
+        <f>IF(Inputs!$B$25&gt;0,MROUND(B29,Inputs!$B$25),B29)</f>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
@@ -3980,16 +4151,16 @@
       </c>
       <c r="B31" s="40">
         <f>B30/B22-1</f>
-        <v>9.4276094276094291E-2</v>
+        <v>3.1096563011456579E-2</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B32" s="40">
         <f>(B30+B28)/B22-1</f>
-        <v>0.15740746643017389</v>
+        <v>0.11292962356792136</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
@@ -3997,46 +4168,46 @@
         <v>8</v>
       </c>
       <c r="B33" s="3" t="str">
-        <f>IF(B26&lt;=0,"NOT RATED",IF(B32&gt;=Inputs!$B$26,"BUY",IF(B32&lt;=Inputs!$B$27,"SELL","HOLD")))</f>
-        <v>BUY</v>
+        <f>IF(B26&lt;=0,"NOT RATED",IF(B32&gt;=Inputs!$B$28,"BUY",IF(B32&lt;=Inputs!$B$29,"SELL","HOLD")))</f>
+        <v>HOLD</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="B37" s="42">
         <f>WACC!$B$17+(-3)*0.005</f>
-        <v>7.0945104064214434E-2</v>
+        <v>7.1002147683209157E-2</v>
       </c>
       <c r="C37" s="42">
         <f>WACC!$B$17+(-2)*0.005</f>
-        <v>7.5945104064214439E-2</v>
+        <v>7.6002147683209162E-2</v>
       </c>
       <c r="D37" s="42">
         <f>WACC!$B$17+(-1)*0.005</f>
-        <v>8.0945104064214429E-2</v>
+        <v>8.1002147683209152E-2</v>
       </c>
       <c r="E37" s="42">
         <f>WACC!$B$17+(0)*0.005</f>
-        <v>8.5945104064214434E-2</v>
+        <v>8.6002147683209157E-2</v>
       </c>
       <c r="F37" s="42">
         <f>WACC!$B$17+(1)*0.005</f>
-        <v>9.0945104064214438E-2</v>
+        <v>9.1002147683209161E-2</v>
       </c>
       <c r="G37" s="42">
         <f>WACC!$B$17+(2)*0.005</f>
-        <v>9.5945104064214429E-2</v>
+        <v>9.6002147683209152E-2</v>
       </c>
       <c r="H37" s="42">
         <f>WACC!$B$17+(3)*0.005</f>
-        <v>0.10094510406421443</v>
+        <v>0.10100214768320916</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
@@ -4045,32 +4216,32 @@
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="B38" s="43">
-        <f>IF(B$37&lt;=$A38,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(B$37-$A38)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>152.23907449365618</v>
+        <f>IF(B$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(B$37-$A38)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>150.55161882732068</v>
       </c>
       <c r="C38" s="43">
-        <f>IF(C$37&lt;=$A38,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(C$37-$A38)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>137.83475797202755</v>
+        <f>IF(C$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(C$37-$A38)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>135.94610474658418</v>
       </c>
       <c r="D38" s="43">
-        <f>IF(D$37&lt;=$A38,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(D$37-$A38)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>125.55436382129041</v>
+        <f>IF(D$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(D$37-$A38)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>123.48581941338513</v>
       </c>
       <c r="E38" s="43">
-        <f>IF(E$37&lt;=$A38,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(E$37-$A38)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>114.96362778819902</v>
+        <f>IF(E$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(E$37-$A38)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>112.73267552570667</v>
       </c>
       <c r="F38" s="43">
-        <f>IF(F$37&lt;=$A38,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(F$37-$A38)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>105.73901833879283</v>
+        <f>IF(F$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(F$37-$A38)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>103.36020561571246</v>
       </c>
       <c r="G38" s="43">
-        <f>IF(G$37&lt;=$A38,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(G$37-$A38)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>97.63456082241315</v>
+        <f>IF(G$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(G$37-$A38)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>95.120143527317296</v>
       </c>
       <c r="H38" s="43">
-        <f>IF(H$37&lt;=$A38,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$20),$G$5*(1+$A38))/(H$37-$A38)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>90.459914682525735</v>
+        <f>IF(H$37&lt;=$A38,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A38)*(1-$A38/Inputs!$B$22),$G$5*(1+$A38))/(H$37-$A38)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>87.820333941575029</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
@@ -4079,32 +4250,32 @@
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="B39" s="43">
-        <f>IF(B$37&lt;=$A39,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(B$37-$A39)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>158.47324385748939</v>
+        <f>IF(B$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(B$37-$A39)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>157.11085595987672</v>
       </c>
       <c r="C39" s="43">
-        <f>IF(C$37&lt;=$A39,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(C$37-$A39)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>142.9851153120986</v>
+        <f>IF(C$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(C$37-$A39)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>141.38430807886178</v>
       </c>
       <c r="D39" s="43">
-        <f>IF(D$37&lt;=$A39,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(D$37-$A39)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>129.86540059557996</v>
+        <f>IF(D$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(D$37-$A39)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>128.05381779414967</v>
       </c>
       <c r="E39" s="43">
-        <f>IF(E$37&lt;=$A39,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(E$37-$A39)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>118.61284932045091</v>
+        <f>IF(E$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(E$37-$A39)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>116.6128887169202</v>
       </c>
       <c r="F39" s="43">
-        <f>IF(F$37&lt;=$A39,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(F$37-$A39)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>108.85822934494168</v>
+        <f>IF(F$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(F$37-$A39)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>106.68831759308165</v>
       </c>
       <c r="G39" s="43">
-        <f>IF(G$37&lt;=$A39,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(G$37-$A39)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>100.32355224545809</v>
+        <f>IF(G$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(G$37-$A39)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>97.999055265431622</v>
       </c>
       <c r="H39" s="43">
-        <f>IF(H$37&lt;=$A39,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$20),$G$5*(1+$A39))/(H$37-$A39)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>92.795531567263808</v>
+        <f>IF(H$37&lt;=$A39,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A39)*(1-$A39/Inputs!$B$22),$G$5*(1+$A39))/(H$37-$A39)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>90.329418114693709</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
@@ -4113,32 +4284,32 @@
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="B40" s="43">
-        <f>IF(B$37&lt;=$A40,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(B$37-$A40)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>165.29064432106404</v>
+        <f>IF(B$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(B$37-$A40)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>164.2830813009991</v>
       </c>
       <c r="C40" s="43">
-        <f>IF(C$37&lt;=$A40,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(C$37-$A40)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>148.5760876038012</v>
+        <f>IF(C$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(C$37-$A40)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>147.28729805125778</v>
       </c>
       <c r="D40" s="43">
-        <f>IF(D$37&lt;=$A40,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(D$37-$A40)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>134.51618279529484</v>
+        <f>IF(D$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(D$37-$A40)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>132.98148892201198</v>
       </c>
       <c r="E40" s="43">
-        <f>IF(E$37&lt;=$A40,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(E$37-$A40)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>122.52865102539334</v>
+        <f>IF(E$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(E$37-$A40)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>120.77632026861187</v>
       </c>
       <c r="F40" s="43">
-        <f>IF(F$37&lt;=$A40,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(F$37-$A40)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>112.18979017657526</v>
+        <f>IF(F$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(F$37-$A40)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>110.24282513046317</v>
       </c>
       <c r="G40" s="43">
-        <f>IF(G$37&lt;=$A40,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(G$37-$A40)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>103.18393686474657</v>
+        <f>IF(G$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(G$37-$A40)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>101.0613321612568</v>
       </c>
       <c r="H40" s="43">
-        <f>IF(H$37&lt;=$A40,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$20),$G$5*(1+$A40))/(H$37-$A40)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>95.271097758251216</v>
+        <f>IF(H$37&lt;=$A40,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A40)*(1-$A40/Inputs!$B$22),$G$5*(1+$A40))/(H$37-$A40)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>92.9887429847725</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
@@ -4147,32 +4318,32 @@
         <v>0.02</v>
       </c>
       <c r="B41" s="43">
-        <f>IF(B$37&lt;=$A41,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(B$37-$A41)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>172.77713758450631</v>
+        <f>IF(B$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(B$37-$A41)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>172.15843637948771</v>
       </c>
       <c r="C41" s="43">
-        <f>IF(C$37&lt;=$A41,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(C$37-$A41)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>154.66674368242514</v>
+        <f>IF(C$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(C$37-$A41)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>153.71732048728248</v>
       </c>
       <c r="D41" s="43">
-        <f>IF(D$37&lt;=$A41,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(D$37-$A41)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>139.5485200248292</v>
+        <f>IF(D$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(D$37-$A41)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>138.31305329912931</v>
       </c>
       <c r="E41" s="44">
-        <f>IF(E$37&lt;=$A41,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(E$37-$A41)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>126.74135132201357</v>
+        <f>IF(E$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(E$37-$A41)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>125.25515303813016</v>
       </c>
       <c r="F41" s="43">
-        <f>IF(F$37&lt;=$A41,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(F$37-$A41)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>115.75614951020397</v>
+        <f>IF(F$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(F$37-$A41)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>114.04764252841682</v>
       </c>
       <c r="G41" s="43">
-        <f>IF(G$37&lt;=$A41,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(G$37-$A41)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>106.23264070846263</v>
+        <f>IF(G$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(G$37-$A41)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>104.32506894928059</v>
       </c>
       <c r="H41" s="43">
-        <f>IF(H$37&lt;=$A41,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$20),$G$5*(1+$A41))/(H$37-$A41)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>97.899580312717717</v>
+        <f>IF(H$37&lt;=$A41,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A41)*(1-$A41/Inputs!$B$22),$G$5*(1+$A41))/(H$37-$A41)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>95.812219358616304</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
@@ -4181,32 +4352,32 @@
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="B42" s="43">
-        <f>IF(B$37&lt;=$A42,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(B$37-$A42)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>181.03630885205797</v>
+        <f>IF(B$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(B$37-$A42)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>180.8456477833835</v>
       </c>
       <c r="C42" s="43">
-        <f>IF(C$37&lt;=$A42,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(C$37-$A42)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>161.32720462767494</v>
+        <f>IF(C$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(C$37-$A42)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>160.74825547677116</v>
       </c>
       <c r="D42" s="43">
-        <f>IF(D$37&lt;=$A42,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(D$37-$A42)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>145.01137554243135</v>
+        <f>IF(D$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(D$37-$A42)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>144.10029021035498</v>
       </c>
       <c r="E42" s="43">
-        <f>IF(E$37&lt;=$A42,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(E$37-$A42)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>131.28604731465757</v>
+        <f>IF(E$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(E$37-$A42)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>130.08663787792656</v>
       </c>
       <c r="F42" s="43">
-        <f>IF(F$37&lt;=$A42,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(F$37-$A42)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>119.58303582983025</v>
+        <f>IF(F$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(F$37-$A42)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>118.13017511681596</v>
       </c>
       <c r="G42" s="43">
-        <f>IF(G$37&lt;=$A42,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(G$37-$A42)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>109.48889438702201</v>
+        <f>IF(G$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(G$37-$A42)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>107.81082216069454</v>
       </c>
       <c r="H42" s="43">
-        <f>IF(H$37&lt;=$A42,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$20),$G$5*(1+$A42))/(H$37-$A42)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>100.69559929828607</v>
+        <f>IF(H$37&lt;=$A42,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A42)*(1-$A42/Inputs!$B$22),$G$5*(1+$A42))/(H$37-$A42)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>98.815530071849011</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
@@ -4215,32 +4386,32 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="B43" s="43">
-        <f>IF(B$37&lt;=$A43,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(B$37-$A43)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>190.19428875610862</v>
+        <f>IF(B$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(B$37-$A43)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>190.47707721202445</v>
       </c>
       <c r="C43" s="43">
-        <f>IF(C$37&lt;=$A43,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(C$37-$A43)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>168.64135556606473</v>
+        <f>IF(C$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(C$37-$A43)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>168.46846879167072</v>
       </c>
       <c r="D43" s="43">
-        <f>IF(D$37&lt;=$A43,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(D$37-$A43)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>150.96246462479124</v>
+        <f>IF(D$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(D$37-$A43)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>150.40422488681307</v>
       </c>
       <c r="E43" s="43">
-        <f>IF(E$37&lt;=$A43,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(E$37-$A43)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>136.2035949138766</v>
+        <f>IF(E$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(E$37-$A43)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>135.31413212257925</v>
       </c>
       <c r="F43" s="43">
-        <f>IF(F$37&lt;=$A43,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(F$37-$A43)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>123.70007911970718</v>
+        <f>IF(F$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(F$37-$A43)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>122.52198041312714</v>
       </c>
       <c r="G43" s="43">
-        <f>IF(G$37&lt;=$A43,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(G$37-$A43)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>112.97463914333161</v>
+        <f>IF(G$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(G$37-$A43)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>111.54204352519635</v>
       </c>
       <c r="H43" s="43">
-        <f>IF(H$37&lt;=$A43,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$20),$G$5*(1+$A43))/(H$37-$A43)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>103.67569986620397</v>
+        <f>IF(H$37&lt;=$A43,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A43)*(1-$A43/Inputs!$B$22),$G$5*(1+$A43))/(H$37-$A43)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>102.01642143278595</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
@@ -4249,32 +4420,32 @@
         <v>2.75E-2</v>
       </c>
       <c r="B44" s="43">
-        <f>IF(B$37&lt;=$A44,"n.m.",(NPV(B$37,$B$5:$G$5)*(1+B$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(B$37-$A44)/(1+B$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>200.40624011463137</v>
+        <f>IF(B$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+B$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+B$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(B$37-$A44)/(1+B$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>201.21551283939147</v>
       </c>
       <c r="C44" s="43">
-        <f>IF(C$37&lt;=$A44,"n.m.",(NPV(C$37,$B$5:$G$5)*(1+C$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(C$37-$A44)/(1+C$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>176.71039712546494</v>
+        <f>IF(C$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+C$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+C$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(C$37-$A44)/(1+C$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>176.98454514394797</v>
       </c>
       <c r="D44" s="43">
-        <f>IF(D$37&lt;=$A44,"n.m.",(NPV(D$37,$B$5:$G$5)*(1+D$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(D$37-$A44)/(1+D$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>157.47030153153645</v>
+        <f>IF(D$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+D$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+D$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(D$37-$A44)/(1+D$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>157.2972886870013</v>
       </c>
       <c r="E44" s="43">
-        <f>IF(E$37&lt;=$A44,"n.m.",(NPV(E$37,$B$5:$G$5)*(1+E$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(E$37-$A44)/(1+E$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>141.54184050636255</v>
+        <f>IF(E$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+E$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+E$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(E$37-$A44)/(1+E$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>140.9884043447654</v>
       </c>
       <c r="F44" s="43">
-        <f>IF(F$37&lt;=$A44,"n.m.",(NPV(F$37,$B$5:$G$5)*(1+F$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(F$37-$A44)/(1+F$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>128.14157954072147</v>
+        <f>IF(F$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+F$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+F$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(F$37-$A44)/(1+F$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>127.25958545452889</v>
       </c>
       <c r="G44" s="43">
-        <f>IF(G$37&lt;=$A44,"n.m.",(NPV(G$37,$B$5:$G$5)*(1+G$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(G$37-$A44)/(1+G$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>116.71502189047831</v>
+        <f>IF(G$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+G$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+G$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(G$37-$A44)/(1+G$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>115.54560827532143</v>
       </c>
       <c r="H44" s="43">
-        <f>IF(H$37&lt;=$A44,"n.m.",(NPV(H$37,$B$5:$G$5)*(1+H$37)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$20),$G$5*(1+$A44))/(H$37-$A44)/(1+H$37)^6-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>106.8586798912272</v>
+        <f>IF(H$37&lt;=$A44,"n.m.",(SUMPRODUCT($B$5:$G$5,(1+H$37)^(-DCF!$B$6:$G$6))-$B$5*Inputs!$B$20*(1+H$37)^(-DCF!$B$6)+IF(Inputs!$B$21=1,Forecast!$H$14*(1+$A44)*(1-$A44/Inputs!$B$22),$G$5*(1+$A44))/(H$37-$A44)/(1+H$37)^(6-Inputs!$B$19)-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>105.43505414290989</v>
       </c>
     </row>
   </sheetData>
@@ -4293,32 +4464,32 @@
   <sheetData>
     <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>10</v>
@@ -4327,15 +4498,15 @@
         <v>11</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B5" s="19">
         <v>0.25</v>
@@ -4352,26 +4523,26 @@
       <c r="F5" s="21">
         <v>-2.5000000000000001E-3</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <f>WACC!$B$17+E5</f>
-        <v>9.0945104064214438E-2</v>
-      </c>
-      <c r="H5" s="33">
+        <v>9.1002147683209161E-2</v>
+      </c>
+      <c r="H5" s="34">
         <f>Inputs!$B$11+F5</f>
         <v>1.7500000000000002E-2</v>
       </c>
       <c r="I5" s="45">
         <f>B25</f>
-        <v>83.957612339117489</v>
-      </c>
-      <c r="J5" s="34">
+        <v>80.666160622216225</v>
+      </c>
+      <c r="J5" s="35">
         <f>I5/Inputs!$B$5-1</f>
-        <v>-0.29328609142156992</v>
+        <v>-0.33988411929446627</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B6" s="19">
         <v>0.5</v>
@@ -4388,26 +4559,26 @@
       <c r="F6" s="21">
         <v>0</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <f>WACC!$B$17+E6</f>
-        <v>8.5945104064214434E-2</v>
-      </c>
-      <c r="H6" s="33">
+        <v>8.6002147683209157E-2</v>
+      </c>
+      <c r="H6" s="34">
         <f>Inputs!$B$11+F6</f>
         <v>0.02</v>
       </c>
       <c r="I6" s="45">
         <f>B40</f>
-        <v>126.74135132201357</v>
-      </c>
-      <c r="J6" s="34">
+        <v>125.25515303813016</v>
+      </c>
+      <c r="J6" s="35">
         <f>I6/Inputs!$B$5-1</f>
-        <v>6.6846391599440835E-2</v>
+        <v>2.5001252357857329E-2</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="B7" s="19">
         <v>0.25</v>
@@ -4424,26 +4595,26 @@
       <c r="F7" s="21">
         <v>2.5000000000000001E-3</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <f>WACC!$B$17+E7</f>
-        <v>8.0945104064214429E-2</v>
-      </c>
-      <c r="H7" s="33">
+        <v>8.1002147683209152E-2</v>
+      </c>
+      <c r="H7" s="34">
         <f>Inputs!$B$11+F7</f>
         <v>2.2499999999999999E-2</v>
       </c>
       <c r="I7" s="45">
         <f>B55</f>
-        <v>186.22650630510276</v>
-      </c>
-      <c r="J7" s="34">
+        <v>187.21054962200435</v>
+      </c>
+      <c r="J7" s="35">
         <f>I7/Inputs!$B$5-1</f>
-        <v>0.56756318438638687</v>
+        <v>0.53200122440265418</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B8" s="40">
         <f>SUM(B5:B7)</f>
@@ -4451,1115 +4622,1115 @@
       </c>
       <c r="I8" s="39">
         <f>IFERROR(SUMPRODUCT(B5:B7,I5:I7)/B8,"")</f>
-        <v>130.91670532206183</v>
+        <v>129.59675408012021</v>
       </c>
       <c r="J8" s="40">
         <f>IFERROR(I8/Inputs!$B$5-1,"")</f>
-        <v>0.10199246904092463</v>
+        <v>6.0529902455975559E-2</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B12" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="26">
-        <f>Inputs!B31+$C$5</f>
-        <v>5.239999599999999E-2</v>
-      </c>
-      <c r="D13" s="26">
-        <f>Inputs!C31+$C$5</f>
+      <c r="A13" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C13" s="27">
+        <f>Inputs!B33+$C$5</f>
+        <v>5.57667260652044E-2</v>
+      </c>
+      <c r="D13" s="27">
+        <f>Inputs!C33+$C$5</f>
         <v>4.0500002999999993E-2</v>
       </c>
-      <c r="E13" s="26">
-        <f>Inputs!D31+$C$5</f>
+      <c r="E13" s="27">
+        <f>Inputs!D33+$C$5</f>
         <v>3.0375002249999988E-2</v>
       </c>
-      <c r="F13" s="26">
-        <f>Inputs!E31+$C$5</f>
+      <c r="F13" s="27">
+        <f>Inputs!E33+$C$5</f>
         <v>2.02500015E-2</v>
       </c>
-      <c r="G13" s="26">
-        <f>Inputs!F31+$C$5</f>
+      <c r="G13" s="27">
+        <f>Inputs!F33+$C$5</f>
         <v>1.0125000749999998E-2</v>
       </c>
-      <c r="H13" s="26">
-        <f>Inputs!G31+$C$5</f>
+      <c r="H13" s="27">
+        <f>Inputs!G33+$C$5</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B14" s="31">
+        <v>89</v>
+      </c>
+      <c r="B14" s="32">
         <f>Forecast!B6</f>
         <v>3944.569</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f t="shared" ref="C14:H14" si="0">B14*(1+C13)</f>
-        <v>4151.2643998217236</v>
-      </c>
-      <c r="D14" s="27">
+        <v>4164.544698868297</v>
+      </c>
+      <c r="D14" s="28">
         <f t="shared" si="0"/>
-        <v>4319.3906204682962</v>
-      </c>
-      <c r="E14" s="27">
+        <v>4333.2087716660972</v>
+      </c>
+      <c r="E14" s="28">
         <f t="shared" si="0"/>
-        <v>4450.5921202836498</v>
-      </c>
-      <c r="F14" s="27">
+        <v>4464.829997855175</v>
+      </c>
+      <c r="F14" s="28">
         <f t="shared" si="0"/>
-        <v>4540.7166173952819</v>
-      </c>
-      <c r="G14" s="27">
+        <v>4555.2428120089871</v>
+      </c>
+      <c r="G14" s="28">
         <f t="shared" si="0"/>
-        <v>4586.6913765519466</v>
-      </c>
-      <c r="H14" s="27">
+        <v>4601.3646488970098</v>
+      </c>
+      <c r="H14" s="28">
         <f t="shared" si="0"/>
-        <v>4586.6913765519466</v>
+        <v>4601.3646488970098</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" s="26">
-        <f>Inputs!B32+$D$5</f>
-        <v>0.11302127279350331</v>
-      </c>
-      <c r="D15" s="26">
-        <f>Inputs!C32+$D$5</f>
-        <v>0.1181158836373742</v>
-      </c>
-      <c r="E15" s="26">
-        <f>Inputs!D32+$D$5</f>
-        <v>0.12321049448124501</v>
-      </c>
-      <c r="F15" s="26">
-        <f>Inputs!E32+$D$5</f>
-        <v>0.1283051053251158</v>
-      </c>
-      <c r="G15" s="26">
-        <f>Inputs!F32+$D$5</f>
-        <v>0.13339971616898672</v>
-      </c>
-      <c r="H15" s="26">
-        <f>Inputs!G32+$D$5</f>
+      <c r="A15" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="27">
+        <f>Inputs!B34+$D$5</f>
+        <v>0.1158433378727224</v>
+      </c>
+      <c r="D15" s="27">
+        <f>Inputs!C34+$D$5</f>
+        <v>0.12037353570074939</v>
+      </c>
+      <c r="E15" s="27">
+        <f>Inputs!D34+$D$5</f>
+        <v>0.1249037335287765</v>
+      </c>
+      <c r="F15" s="27">
+        <f>Inputs!E34+$D$5</f>
+        <v>0.12943393135680348</v>
+      </c>
+      <c r="G15" s="27">
+        <f>Inputs!F34+$D$5</f>
+        <v>0.13396412918483053</v>
+      </c>
+      <c r="H15" s="27">
+        <f>Inputs!G34+$D$5</f>
         <v>0.13849432701285752</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="27">
+        <v>93</v>
+      </c>
+      <c r="C16" s="28">
         <f t="shared" ref="C16:H16" si="1">C14*C15</f>
-        <v>469.1811861702098</v>
-      </c>
-      <c r="D16" s="27">
+        <v>482.4347586370551</v>
+      </c>
+      <c r="D16" s="28">
         <f t="shared" si="1"/>
-        <v>510.18863991159884</v>
-      </c>
-      <c r="E16" s="27">
+        <v>521.60366077494939</v>
+      </c>
+      <c r="E16" s="28">
         <f t="shared" si="1"/>
-        <v>548.35965587448118</v>
-      </c>
-      <c r="F16" s="27">
+        <v>557.67393630339052</v>
+      </c>
+      <c r="F16" s="28">
         <f t="shared" si="1"/>
-        <v>582.59712384640522</v>
-      </c>
-      <c r="G16" s="27">
+        <v>589.60298544314367</v>
+      </c>
+      <c r="G16" s="28">
         <f t="shared" si="1"/>
-        <v>611.86332778676865</v>
-      </c>
-      <c r="H16" s="27">
+        <v>616.4178082513514</v>
+      </c>
+      <c r="H16" s="28">
         <f t="shared" si="1"/>
-        <v>635.23073541123892</v>
+        <v>637.2629003897448</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C17" s="28">
-        <f>C14*Inputs!B33</f>
-        <v>141.61242584957719</v>
-      </c>
-      <c r="D17" s="28">
-        <f>D14*Inputs!C33</f>
-        <v>147.34772952132232</v>
-      </c>
-      <c r="E17" s="28">
-        <f>E14*Inputs!D33</f>
-        <v>151.82341713706489</v>
-      </c>
-      <c r="F17" s="28">
-        <f>F14*Inputs!E33</f>
-        <v>154.89784156182557</v>
-      </c>
-      <c r="G17" s="28">
-        <f>G14*Inputs!F33</f>
-        <v>156.46618232381243</v>
-      </c>
-      <c r="H17" s="28">
-        <f>H14*Inputs!G33</f>
-        <v>156.46618232381243</v>
+        <v>96</v>
+      </c>
+      <c r="C17" s="29">
+        <f>C14*Inputs!B35</f>
+        <v>142.06545778945406</v>
+      </c>
+      <c r="D17" s="29">
+        <f>D14*Inputs!C35</f>
+        <v>147.81910925612334</v>
+      </c>
+      <c r="E17" s="29">
+        <f>E14*Inputs!D35</f>
+        <v>152.3091150323711</v>
+      </c>
+      <c r="F17" s="29">
+        <f>F14*Inputs!E35</f>
+        <v>155.39337484024026</v>
+      </c>
+      <c r="G17" s="29">
+        <f>G14*Inputs!F35</f>
+        <v>156.96673287704272</v>
+      </c>
+      <c r="H17" s="29">
+        <f>H14*Inputs!G35</f>
+        <v>156.96673287704272</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" s="28">
+        <v>97</v>
+      </c>
+      <c r="C18" s="29">
         <f t="shared" ref="C18:H18" si="2">C16-C17</f>
-        <v>327.56876032063258</v>
-      </c>
-      <c r="D18" s="28">
+        <v>340.36930084760104</v>
+      </c>
+      <c r="D18" s="29">
         <f t="shared" si="2"/>
-        <v>362.84091039027652</v>
-      </c>
-      <c r="E18" s="28">
+        <v>373.78455151882605</v>
+      </c>
+      <c r="E18" s="29">
         <f t="shared" si="2"/>
-        <v>396.53623873741628</v>
-      </c>
-      <c r="F18" s="28">
+        <v>405.36482127101942</v>
+      </c>
+      <c r="F18" s="29">
         <f t="shared" si="2"/>
-        <v>427.69928228457968</v>
-      </c>
-      <c r="G18" s="28">
+        <v>434.20961060290341</v>
+      </c>
+      <c r="G18" s="29">
         <f t="shared" si="2"/>
-        <v>455.39714546295625</v>
-      </c>
-      <c r="H18" s="28">
+        <v>459.45107537430869</v>
+      </c>
+      <c r="H18" s="29">
         <f t="shared" si="2"/>
-        <v>478.76455308742652</v>
+        <v>480.29616751270208</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="28">
+        <v>116</v>
+      </c>
+      <c r="C19" s="29">
         <f>-MAX(C18,0)*Inputs!$B$10</f>
-        <v>-72.065127270539165</v>
-      </c>
-      <c r="D19" s="28">
+        <v>-74.881246186472225</v>
+      </c>
+      <c r="D19" s="29">
         <f>-MAX(D18,0)*Inputs!$B$10</f>
-        <v>-79.825000285860838</v>
-      </c>
-      <c r="E19" s="28">
+        <v>-82.232601334141734</v>
+      </c>
+      <c r="E19" s="29">
         <f>-MAX(E18,0)*Inputs!$B$10</f>
-        <v>-87.237972522231587</v>
-      </c>
-      <c r="F19" s="28">
+        <v>-89.180260679624269</v>
+      </c>
+      <c r="F19" s="29">
         <f>-MAX(F18,0)*Inputs!$B$10</f>
-        <v>-94.093842102607525</v>
-      </c>
-      <c r="G19" s="28">
+        <v>-95.526114332638755</v>
+      </c>
+      <c r="G19" s="29">
         <f>-MAX(G18,0)*Inputs!$B$10</f>
-        <v>-100.18737200185038</v>
-      </c>
-      <c r="H19" s="28">
+        <v>-101.07923658234792</v>
+      </c>
+      <c r="H19" s="29">
         <f>-MAX(H18,0)*Inputs!$B$10</f>
-        <v>-105.32820167923383</v>
+        <v>-105.66515685279445</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" s="28">
+        <v>100</v>
+      </c>
+      <c r="C20" s="29">
         <f t="shared" ref="C20:H20" si="3">C18+C19</f>
-        <v>255.50363305009341</v>
-      </c>
-      <c r="D20" s="28">
+        <v>265.48805466112879</v>
+      </c>
+      <c r="D20" s="29">
         <f t="shared" si="3"/>
-        <v>283.0159101044157</v>
-      </c>
-      <c r="E20" s="28">
+        <v>291.5519501846843</v>
+      </c>
+      <c r="E20" s="29">
         <f t="shared" si="3"/>
-        <v>309.2982662151847</v>
-      </c>
-      <c r="F20" s="28">
+        <v>316.18456059139515</v>
+      </c>
+      <c r="F20" s="29">
         <f t="shared" si="3"/>
-        <v>333.60544018197214</v>
-      </c>
-      <c r="G20" s="28">
+        <v>338.68349627026464</v>
+      </c>
+      <c r="G20" s="29">
         <f t="shared" si="3"/>
-        <v>355.2097734611059</v>
-      </c>
-      <c r="H20" s="28">
+        <v>358.37183879196078</v>
+      </c>
+      <c r="H20" s="29">
         <f t="shared" si="3"/>
-        <v>373.43635140819271</v>
+        <v>374.63101065990764</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="28">
-        <f>-C14*Inputs!B34</f>
-        <v>-231.63830054955054</v>
-      </c>
-      <c r="D21" s="28">
-        <f>-D14*Inputs!C34</f>
-        <v>-223.75874513285541</v>
-      </c>
-      <c r="E21" s="28">
-        <f>-E14*Inputs!D34</f>
-        <v>-212.77021013827186</v>
-      </c>
-      <c r="F21" s="28">
-        <f>-F14*Inputs!E34</f>
-        <v>-198.93344935512374</v>
-      </c>
-      <c r="G21" s="28">
-        <f>-G14*Inputs!F34</f>
-        <v>-182.61857105952379</v>
-      </c>
-      <c r="H21" s="28">
-        <f>-H14*Inputs!G34</f>
-        <v>-164.28949144000308</v>
+        <v>101</v>
+      </c>
+      <c r="C21" s="29">
+        <f>-C14*Inputs!B36</f>
+        <v>-232.37933402890931</v>
+      </c>
+      <c r="D21" s="29">
+        <f>-D14*Inputs!C36</f>
+        <v>-224.47457114716036</v>
+      </c>
+      <c r="E21" s="29">
+        <f>-E14*Inputs!D36</f>
+        <v>-213.45088275911479</v>
+      </c>
+      <c r="F21" s="29">
+        <f>-F14*Inputs!E36</f>
+        <v>-199.56985683085955</v>
+      </c>
+      <c r="G21" s="29">
+        <f>-G14*Inputs!F36</f>
+        <v>-183.20278565092212</v>
+      </c>
+      <c r="H21" s="29">
+        <f>-H14*Inputs!G36</f>
+        <v>-164.81506952089487</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="28">
-        <f>-Inputs!B35*(C14-B14)</f>
-        <v>-8.0589314228409599</v>
-      </c>
-      <c r="D22" s="28">
-        <f>-Inputs!C35*(D14-C14)</f>
-        <v>-6.5551419322383735</v>
-      </c>
-      <c r="E22" s="28">
-        <f>-Inputs!D35*(E14-D14)</f>
-        <v>-5.115468900119609</v>
-      </c>
-      <c r="F22" s="28">
-        <f>-Inputs!E35*(F14-E14)</f>
-        <v>-3.5139008529803593</v>
-      </c>
-      <c r="G22" s="28">
-        <f>-Inputs!F35*(G14-F14)</f>
-        <v>-1.7925286752620331</v>
-      </c>
-      <c r="H22" s="28">
-        <f>-Inputs!G35*(H14-G14)</f>
+        <v>102</v>
+      </c>
+      <c r="C22" s="29">
+        <f>-Inputs!B37*(C14-B14)</f>
+        <v>-8.576722430204768</v>
+      </c>
+      <c r="D22" s="29">
+        <f>-Inputs!C37*(D14-C14)</f>
+        <v>-6.5761124695899964</v>
+      </c>
+      <c r="E22" s="29">
+        <f>-Inputs!D37*(E14-D14)</f>
+        <v>-5.13183378325256</v>
+      </c>
+      <c r="F22" s="29">
+        <f>-Inputs!E37*(F14-E14)</f>
+        <v>-3.5251421639769744</v>
+      </c>
+      <c r="G22" s="29">
+        <f>-Inputs!F37*(G14-F14)</f>
+        <v>-1.7982631490425971</v>
+      </c>
+      <c r="H22" s="29">
+        <f>-Inputs!G37*(H14-G14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C23" s="27">
+        <v>103</v>
+      </c>
+      <c r="C23" s="28">
         <f t="shared" ref="C23:H23" si="4">C20+C17+C21+C22</f>
-        <v>157.41882692727913</v>
-      </c>
-      <c r="D23" s="27">
+        <v>166.59745599146876</v>
+      </c>
+      <c r="D23" s="28">
         <f t="shared" si="4"/>
-        <v>200.04975256064424</v>
-      </c>
-      <c r="E23" s="27">
+        <v>208.32037582405729</v>
+      </c>
+      <c r="E23" s="28">
         <f t="shared" si="4"/>
-        <v>243.23600431385813</v>
-      </c>
-      <c r="F23" s="27">
+        <v>249.91095908139891</v>
+      </c>
+      <c r="F23" s="28">
         <f t="shared" si="4"/>
-        <v>286.05593153569362</v>
-      </c>
-      <c r="G23" s="27">
+        <v>290.98187211566835</v>
+      </c>
+      <c r="G23" s="28">
         <f t="shared" si="4"/>
-        <v>327.26485605013249</v>
-      </c>
-      <c r="H23" s="27">
+        <v>330.33752286903876</v>
+      </c>
+      <c r="H23" s="28">
         <f t="shared" si="4"/>
-        <v>365.61304229200209</v>
+        <v>366.78267401605547</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="28">
-        <f>NPV($G$5,$C$23:$H$23)*(1+$G$5)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$20*(1+$H$5)*(1-$H$5/Inputs!$B$20),$H$23*(1+$H$5))/($G$5-$H$5)/(1+$G$5)^6</f>
-        <v>4134.842754656629</v>
+        <v>141</v>
+      </c>
+      <c r="B24" s="29">
+        <f>SUMPRODUCT($C$23:$H$23,(1+$G$5)^(-DCF!$B$6:$G$6))-$C$23*Inputs!$B$20*(1+$G$5)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$20*(1+$H$5)*(1-$H$5/Inputs!$B$22),$H$23*(1+$H$5))/($G$5-$H$5)/(1+$G$5)^(6-Inputs!$B$19)</f>
+        <v>4359.8981664079993</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B25" s="45">
         <f>(B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>83.957612339117489</v>
+        <v>80.666160622216225</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="B27" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H27" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A28" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="26">
-        <f>Inputs!B31+$C$6</f>
-        <v>7.2399995999999994E-2</v>
-      </c>
-      <c r="D28" s="26">
-        <f>Inputs!C31+$C$6</f>
+      <c r="A28" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="27">
+        <f>Inputs!B33+$C$6</f>
+        <v>7.5766726065204404E-2</v>
+      </c>
+      <c r="D28" s="27">
+        <f>Inputs!C33+$C$6</f>
         <v>6.0500002999999997E-2</v>
       </c>
-      <c r="E28" s="26">
-        <f>Inputs!D31+$C$6</f>
+      <c r="E28" s="27">
+        <f>Inputs!D33+$C$6</f>
         <v>5.0375002249999988E-2</v>
       </c>
-      <c r="F28" s="26">
-        <f>Inputs!E31+$C$6</f>
+      <c r="F28" s="27">
+        <f>Inputs!E33+$C$6</f>
         <v>4.02500015E-2</v>
       </c>
-      <c r="G28" s="26">
-        <f>Inputs!F31+$C$6</f>
+      <c r="G28" s="27">
+        <f>Inputs!F33+$C$6</f>
         <v>3.0125000749999999E-2</v>
       </c>
-      <c r="H28" s="26">
-        <f>Inputs!G31+$C$6</f>
+      <c r="H28" s="27">
+        <f>Inputs!G33+$C$6</f>
         <v>0.02</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="31">
+        <v>89</v>
+      </c>
+      <c r="B29" s="32">
         <f>Forecast!B6</f>
         <v>3944.569</v>
       </c>
-      <c r="C29" s="27">
+      <c r="C29" s="28">
         <f t="shared" ref="C29:H29" si="5">B29*(1+C28)</f>
-        <v>4230.1557798217236</v>
-      </c>
-      <c r="D29" s="27">
+        <v>4243.436078868297</v>
+      </c>
+      <c r="D29" s="28">
         <f t="shared" si="5"/>
-        <v>4486.0802171914056</v>
-      </c>
-      <c r="E29" s="27">
+        <v>4500.1639743701371</v>
+      </c>
+      <c r="E29" s="28">
         <f t="shared" si="5"/>
-        <v>4712.0665182261037</v>
-      </c>
-      <c r="F29" s="27">
+        <v>4726.8597447044021</v>
+      </c>
+      <c r="F29" s="28">
         <f t="shared" si="5"/>
-        <v>4901.7272026528044</v>
-      </c>
-      <c r="G29" s="27">
+        <v>4917.1158565190444</v>
+      </c>
+      <c r="G29" s="28">
         <f t="shared" si="5"/>
-        <v>5049.3917383090156</v>
-      </c>
-      <c r="H29" s="27">
+        <v>5065.2439753845174</v>
+      </c>
+      <c r="H29" s="28">
         <f t="shared" si="5"/>
-        <v>5150.3795730751963</v>
+        <v>5166.5488548922076</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A30" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="26">
-        <f>Inputs!B32+$D$6</f>
-        <v>0.12802127279350331</v>
-      </c>
-      <c r="D30" s="26">
-        <f>Inputs!C32+$D$6</f>
-        <v>0.1331158836373742</v>
-      </c>
-      <c r="E30" s="26">
-        <f>Inputs!D32+$D$6</f>
-        <v>0.13821049448124501</v>
-      </c>
-      <c r="F30" s="26">
-        <f>Inputs!E32+$D$6</f>
-        <v>0.14330510532511581</v>
-      </c>
-      <c r="G30" s="26">
-        <f>Inputs!F32+$D$6</f>
-        <v>0.1483997161689867</v>
-      </c>
-      <c r="H30" s="26">
-        <f>Inputs!G32+$D$6</f>
+      <c r="A30" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C30" s="27">
+        <f>Inputs!B34+$D$6</f>
+        <v>0.1308433378727224</v>
+      </c>
+      <c r="D30" s="27">
+        <f>Inputs!C34+$D$6</f>
+        <v>0.13537353570074939</v>
+      </c>
+      <c r="E30" s="27">
+        <f>Inputs!D34+$D$6</f>
+        <v>0.1399037335287765</v>
+      </c>
+      <c r="F30" s="27">
+        <f>Inputs!E34+$D$6</f>
+        <v>0.14443393135680349</v>
+      </c>
+      <c r="G30" s="27">
+        <f>Inputs!F34+$D$6</f>
+        <v>0.14896412918483051</v>
+      </c>
+      <c r="H30" s="27">
+        <f>Inputs!G34+$D$6</f>
         <v>0.15349432701285751</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="27">
+        <v>93</v>
+      </c>
+      <c r="C31" s="28">
         <f t="shared" ref="C31:H31" si="6">C29*C30</f>
-        <v>541.5499270475716</v>
-      </c>
-      <c r="D31" s="27">
+        <v>555.22534060866485</v>
+      </c>
+      <c r="D31" s="28">
         <f t="shared" si="6"/>
-        <v>597.16853217957748</v>
-      </c>
-      <c r="E31" s="27">
+        <v>609.203108443622</v>
+      </c>
+      <c r="E31" s="28">
         <f t="shared" si="6"/>
-        <v>651.25704351254831</v>
-      </c>
-      <c r="F31" s="27">
+        <v>661.30532615102516</v>
+      </c>
+      <c r="F31" s="28">
         <f t="shared" si="6"/>
-        <v>702.44253305114546</v>
-      </c>
-      <c r="G31" s="27">
+        <v>710.19837409392164</v>
+      </c>
+      <c r="G31" s="28">
         <f t="shared" si="6"/>
-        <v>749.3283007910843</v>
-      </c>
-      <c r="H31" s="27">
+        <v>754.53965790186373</v>
+      </c>
+      <c r="H31" s="28">
         <f t="shared" si="6"/>
-        <v>790.55404642994563</v>
+        <v>793.03593946072897</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="28">
-        <f>C29*Inputs!B33</f>
-        <v>144.30365402114356</v>
-      </c>
-      <c r="D32" s="28">
-        <f>D29*Inputs!C33</f>
-        <v>153.03402552233374</v>
-      </c>
-      <c r="E32" s="28">
-        <f>E29*Inputs!D33</f>
-        <v>160.74311490234786</v>
-      </c>
-      <c r="F32" s="28">
-        <f>F29*Inputs!E33</f>
-        <v>167.21302551828205</v>
-      </c>
-      <c r="G32" s="28">
-        <f>G29*Inputs!F33</f>
-        <v>172.25031803743005</v>
-      </c>
-      <c r="H32" s="28">
-        <f>H29*Inputs!G33</f>
-        <v>175.69532439817868</v>
+        <v>96</v>
+      </c>
+      <c r="C32" s="29">
+        <f>C29*Inputs!B35</f>
+        <v>144.75668596102045</v>
+      </c>
+      <c r="D32" s="29">
+        <f>D29*Inputs!C35</f>
+        <v>153.51446589593223</v>
+      </c>
+      <c r="E32" s="29">
+        <f>E29*Inputs!D35</f>
+        <v>161.2477574608474</v>
+      </c>
+      <c r="F32" s="29">
+        <f>F29*Inputs!E35</f>
+        <v>167.73797994051816</v>
+      </c>
+      <c r="G32" s="29">
+        <f>G29*Inputs!F35</f>
+        <v>172.79108671202974</v>
+      </c>
+      <c r="H32" s="29">
+        <f>H29*Inputs!G35</f>
+        <v>176.24690844627034</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="28">
+        <v>97</v>
+      </c>
+      <c r="C33" s="29">
         <f t="shared" ref="C33:H33" si="7">C31-C32</f>
-        <v>397.24627302642807</v>
-      </c>
-      <c r="D33" s="28">
+        <v>410.46865464764437</v>
+      </c>
+      <c r="D33" s="29">
         <f t="shared" si="7"/>
-        <v>444.13450665724372</v>
-      </c>
-      <c r="E33" s="28">
+        <v>455.68864254768977</v>
+      </c>
+      <c r="E33" s="29">
         <f t="shared" si="7"/>
-        <v>490.51392861020042</v>
-      </c>
-      <c r="F33" s="28">
+        <v>500.05756869017773</v>
+      </c>
+      <c r="F33" s="29">
         <f t="shared" si="7"/>
-        <v>535.22950753286341</v>
-      </c>
-      <c r="G33" s="28">
+        <v>542.46039415340351</v>
+      </c>
+      <c r="G33" s="29">
         <f t="shared" si="7"/>
-        <v>577.07798275365428</v>
-      </c>
-      <c r="H33" s="28">
+        <v>581.74857118983402</v>
+      </c>
+      <c r="H33" s="29">
         <f t="shared" si="7"/>
-        <v>614.858722031767</v>
+        <v>616.7890310144586</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C34" s="28">
+        <v>116</v>
+      </c>
+      <c r="C34" s="29">
         <f>-MAX(C33,0)*Inputs!$B$10</f>
-        <v>-87.394180065814183</v>
-      </c>
-      <c r="D34" s="28">
+        <v>-90.303104022481762</v>
+      </c>
+      <c r="D34" s="29">
         <f>-MAX(D33,0)*Inputs!$B$10</f>
-        <v>-97.709591464593615</v>
-      </c>
-      <c r="E34" s="28">
+        <v>-100.25150136049174</v>
+      </c>
+      <c r="E34" s="29">
         <f>-MAX(E33,0)*Inputs!$B$10</f>
-        <v>-107.91306429424409</v>
-      </c>
-      <c r="F34" s="28">
+        <v>-110.0126651118391</v>
+      </c>
+      <c r="F34" s="29">
         <f>-MAX(F33,0)*Inputs!$B$10</f>
-        <v>-117.75049165722994</v>
-      </c>
-      <c r="G34" s="28">
+        <v>-119.34128671374877</v>
+      </c>
+      <c r="G34" s="29">
         <f>-MAX(G33,0)*Inputs!$B$10</f>
-        <v>-126.95715620580394</v>
-      </c>
-      <c r="H34" s="28">
+        <v>-127.98468566176349</v>
+      </c>
+      <c r="H34" s="29">
         <f>-MAX(H33,0)*Inputs!$B$10</f>
-        <v>-135.26891884698875</v>
+        <v>-135.69358682318088</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="28">
+        <v>100</v>
+      </c>
+      <c r="C35" s="29">
         <f t="shared" ref="C35:H35" si="8">C33+C34</f>
-        <v>309.8520929606139</v>
-      </c>
-      <c r="D35" s="28">
+        <v>320.16555062516261</v>
+      </c>
+      <c r="D35" s="29">
         <f t="shared" si="8"/>
-        <v>346.42491519265013</v>
-      </c>
-      <c r="E35" s="28">
+        <v>355.43714118719799</v>
+      </c>
+      <c r="E35" s="29">
         <f t="shared" si="8"/>
-        <v>382.6008643159563</v>
-      </c>
-      <c r="F35" s="28">
+        <v>390.04490357833862</v>
+      </c>
+      <c r="F35" s="29">
         <f t="shared" si="8"/>
-        <v>417.47901587563348</v>
-      </c>
-      <c r="G35" s="28">
+        <v>423.11910743965473</v>
+      </c>
+      <c r="G35" s="29">
         <f t="shared" si="8"/>
-        <v>450.12082654785036</v>
-      </c>
-      <c r="H35" s="28">
+        <v>453.76388552807055</v>
+      </c>
+      <c r="H35" s="29">
         <f t="shared" si="8"/>
-        <v>479.58980318477825</v>
+        <v>481.09544419127769</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="28">
-        <f>-C29*Inputs!B34</f>
-        <v>-236.04039673788139</v>
-      </c>
-      <c r="D36" s="28">
-        <f>-D29*Inputs!C34</f>
-        <v>-232.39381851860557</v>
-      </c>
-      <c r="E36" s="28">
-        <f>-E29*Inputs!D34</f>
-        <v>-225.27056089889118</v>
-      </c>
-      <c r="F36" s="28">
-        <f>-F29*Inputs!E34</f>
-        <v>-214.74969314005031</v>
-      </c>
-      <c r="G36" s="28">
-        <f>-G29*Inputs!F34</f>
-        <v>-201.0409308731291</v>
-      </c>
-      <c r="H36" s="28">
-        <f>-H29*Inputs!G34</f>
-        <v>-184.48009061808762</v>
+        <v>101</v>
+      </c>
+      <c r="C36" s="29">
+        <f>-C29*Inputs!B36</f>
+        <v>-236.78143021724017</v>
+      </c>
+      <c r="D36" s="29">
+        <f>-D29*Inputs!C36</f>
+        <v>-233.12340380272769</v>
+      </c>
+      <c r="E36" s="29">
+        <f>-E29*Inputs!D36</f>
+        <v>-225.97778317883581</v>
+      </c>
+      <c r="F36" s="29">
+        <f>-F29*Inputs!E36</f>
+        <v>-215.42388583968179</v>
+      </c>
+      <c r="G36" s="29">
+        <f>-G29*Inputs!F36</f>
+        <v>-201.67208580490069</v>
+      </c>
+      <c r="H36" s="29">
+        <f>-H29*Inputs!G36</f>
+        <v>-185.05925386858385</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C37" s="28">
-        <f>-Inputs!B35*(C29-B29)</f>
-        <v>-11.134859681629749</v>
-      </c>
-      <c r="D37" s="28">
-        <f>-Inputs!C35*(D29-C29)</f>
-        <v>-9.9783424883685168</v>
-      </c>
-      <c r="E37" s="28">
-        <f>-Inputs!D35*(E29-D29)</f>
-        <v>-8.8110722546845768</v>
-      </c>
-      <c r="F37" s="28">
-        <f>-Inputs!E35*(F29-E29)</f>
-        <v>-7.3947579419869642</v>
-      </c>
-      <c r="G37" s="28">
-        <f>-Inputs!F35*(G29-F29)</f>
-        <v>-5.7573529331831281</v>
-      </c>
-      <c r="H37" s="28">
-        <f>-Inputs!G35*(H29-G29)</f>
-        <v>-3.93745596478586</v>
+        <v>102</v>
+      </c>
+      <c r="C37" s="29">
+        <f>-Inputs!B37*(C29-B29)</f>
+        <v>-11.652650688993557</v>
+      </c>
+      <c r="D37" s="29">
+        <f>-Inputs!C37*(D29-C29)</f>
+        <v>-10.009668845867381</v>
+      </c>
+      <c r="E37" s="29">
+        <f>-Inputs!D37*(E29-D29)</f>
+        <v>-8.8387340431750463</v>
+      </c>
+      <c r="F37" s="29">
+        <f>-Inputs!E37*(F29-E29)</f>
+        <v>-7.4179733037746036</v>
+      </c>
+      <c r="G37" s="29">
+        <f>-Inputs!F37*(G29-F29)</f>
+        <v>-5.7754277684017312</v>
+      </c>
+      <c r="H37" s="29">
+        <f>-Inputs!G37*(H29-G29)</f>
+        <v>-3.9498173517930288</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C38" s="27">
+        <v>103</v>
+      </c>
+      <c r="C38" s="28">
         <f t="shared" ref="C38:H38" si="9">C35+C32+C36+C37</f>
-        <v>206.98049056224636</v>
-      </c>
-      <c r="D38" s="27">
+        <v>216.48815567994936</v>
+      </c>
+      <c r="D38" s="28">
         <f t="shared" si="9"/>
-        <v>257.08677970800977</v>
-      </c>
-      <c r="E38" s="27">
+        <v>265.81853443453514</v>
+      </c>
+      <c r="E38" s="28">
         <f t="shared" si="9"/>
-        <v>309.26234606472843</v>
-      </c>
-      <c r="F38" s="27">
+        <v>316.47614381717511</v>
+      </c>
+      <c r="F38" s="28">
         <f t="shared" si="9"/>
-        <v>362.54759031187831</v>
-      </c>
-      <c r="G38" s="27">
+        <v>368.01522823671644</v>
+      </c>
+      <c r="G38" s="28">
         <f t="shared" si="9"/>
-        <v>415.57286077896811</v>
-      </c>
-      <c r="H38" s="27">
+        <v>419.10745866679781</v>
+      </c>
+      <c r="H38" s="28">
         <f t="shared" si="9"/>
-        <v>466.86758100008342</v>
+        <v>468.33328141717124</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B39" s="28">
-        <f>NPV($G$6,$C$38:$H$38)*(1+$G$6)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$35*(1+$H$6)*(1-$H$6/Inputs!$B$20),$H$38*(1+$H$6))/($G$6-$H$6)/(1+$G$6)^6</f>
-        <v>5873.794756582156</v>
+        <v>141</v>
+      </c>
+      <c r="B39" s="29">
+        <f>SUMPRODUCT($C$38:$H$38,(1+$G$6)^(-DCF!$B$6:$G$6))-$C$38*Inputs!$B$20*(1+$G$6)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$35*(1+$H$6)*(1-$H$6/Inputs!$B$22),$H$38*(1+$H$6))/($G$6-$H$6)/(1+$G$6)^(6-Inputs!$B$19)</f>
+        <v>6172.2249865695921</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B40" s="45">
         <f>(B39-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>126.74135132201357</v>
+        <v>125.25515303813016</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B42" s="46" t="str">
         <f>Forecast!B4</f>
         <v>2025A</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H42" s="14" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A43" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="C43" s="26">
-        <f>Inputs!B31+$C$7</f>
-        <v>9.2399995999999998E-2</v>
-      </c>
-      <c r="D43" s="26">
-        <f>Inputs!C31+$C$7</f>
+      <c r="A43" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="27">
+        <f>Inputs!B33+$C$7</f>
+        <v>9.5766726065204408E-2</v>
+      </c>
+      <c r="D43" s="27">
+        <f>Inputs!C33+$C$7</f>
         <v>8.0500003000000001E-2</v>
       </c>
-      <c r="E43" s="26">
-        <f>Inputs!D31+$C$7</f>
+      <c r="E43" s="27">
+        <f>Inputs!D33+$C$7</f>
         <v>7.0375002249999985E-2</v>
       </c>
-      <c r="F43" s="26">
-        <f>Inputs!E31+$C$7</f>
+      <c r="F43" s="27">
+        <f>Inputs!E33+$C$7</f>
         <v>6.0250001499999997E-2</v>
       </c>
-      <c r="G43" s="26">
-        <f>Inputs!F31+$C$7</f>
+      <c r="G43" s="27">
+        <f>Inputs!F33+$C$7</f>
         <v>5.0125000749999996E-2</v>
       </c>
-      <c r="H43" s="26">
-        <f>Inputs!G31+$C$7</f>
+      <c r="H43" s="27">
+        <f>Inputs!G33+$C$7</f>
         <v>0.04</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B44" s="31">
+        <v>89</v>
+      </c>
+      <c r="B44" s="32">
         <f>Forecast!B6</f>
         <v>3944.569</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C44" s="28">
         <f t="shared" ref="C44:H44" si="10">B44*(1+C43)</f>
-        <v>4309.0471598217237</v>
-      </c>
-      <c r="D44" s="27">
+        <v>4322.3274588682971</v>
+      </c>
+      <c r="D44" s="28">
         <f t="shared" si="10"/>
-        <v>4655.9254691145143</v>
-      </c>
-      <c r="E44" s="27">
+        <v>4670.2748322741772</v>
+      </c>
+      <c r="E44" s="28">
         <f t="shared" si="10"/>
-        <v>4983.5862344792804</v>
-      </c>
-      <c r="F44" s="27">
+        <v>4998.9454341035907</v>
+      </c>
+      <c r="F44" s="28">
         <f t="shared" si="10"/>
-        <v>5283.8473125820365</v>
-      </c>
-      <c r="G44" s="27">
+        <v>5300.1319040067501</v>
+      </c>
+      <c r="G44" s="28">
         <f t="shared" si="10"/>
-        <v>5548.7001630880968</v>
-      </c>
-      <c r="H44" s="27">
+        <v>5565.801019670188</v>
+      </c>
+      <c r="H44" s="28">
         <f t="shared" si="10"/>
-        <v>5770.6481696116207</v>
+        <v>5788.4330604569959</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A45" s="25" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="26">
-        <f>Inputs!B32+$D$7</f>
-        <v>0.1430212727935033</v>
-      </c>
-      <c r="D45" s="26">
-        <f>Inputs!C32+$D$7</f>
-        <v>0.14811588363737421</v>
-      </c>
-      <c r="E45" s="26">
-        <f>Inputs!D32+$D$7</f>
-        <v>0.15321049448124502</v>
-      </c>
-      <c r="F45" s="26">
-        <f>Inputs!E32+$D$7</f>
-        <v>0.15830510532511582</v>
-      </c>
-      <c r="G45" s="26">
-        <f>Inputs!F32+$D$7</f>
-        <v>0.16339971616898669</v>
-      </c>
-      <c r="H45" s="26">
-        <f>Inputs!G32+$D$7</f>
+      <c r="A45" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="27">
+        <f>Inputs!B34+$D$7</f>
+        <v>0.14584333787272241</v>
+      </c>
+      <c r="D45" s="27">
+        <f>Inputs!C34+$D$7</f>
+        <v>0.15037353570074941</v>
+      </c>
+      <c r="E45" s="27">
+        <f>Inputs!D34+$D$7</f>
+        <v>0.15490373352877651</v>
+      </c>
+      <c r="F45" s="27">
+        <f>Inputs!E34+$D$7</f>
+        <v>0.1594339313568035</v>
+      </c>
+      <c r="G45" s="27">
+        <f>Inputs!F34+$D$7</f>
+        <v>0.1639641291848305</v>
+      </c>
+      <c r="H45" s="27">
+        <f>Inputs!G34+$D$7</f>
         <v>0.16849432701285749</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="27">
+        <v>93</v>
+      </c>
+      <c r="C46" s="28">
         <f t="shared" ref="C46:H46" si="11">C44*C45</f>
-        <v>616.28540932493331</v>
-      </c>
-      <c r="D46" s="27">
+        <v>630.38266398027474</v>
+      </c>
+      <c r="D46" s="28">
         <f t="shared" si="11"/>
-        <v>689.61651500765231</v>
-      </c>
-      <c r="E46" s="27">
+        <v>702.28573922329247</v>
+      </c>
+      <c r="E46" s="28">
         <f t="shared" si="11"/>
-        <v>763.53771127449647</v>
-      </c>
-      <c r="F46" s="27">
+        <v>774.35531144927666</v>
+      </c>
+      <c r="F46" s="28">
         <f t="shared" si="11"/>
-        <v>836.46000534012944</v>
-      </c>
-      <c r="G46" s="27">
+        <v>845.02086616541646</v>
+      </c>
+      <c r="G46" s="28">
         <f t="shared" si="11"/>
-        <v>906.65603175540514</v>
-      </c>
-      <c r="H46" s="27">
+        <v>912.59171740626402</v>
+      </c>
+      <c r="H46" s="28">
         <f t="shared" si="11"/>
-        <v>972.32147976668796</v>
+        <v>975.31813298067652</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="28">
-        <f>C44*Inputs!B33</f>
-        <v>146.99488219270995</v>
-      </c>
-      <c r="D47" s="28">
-        <f>D44*Inputs!C33</f>
-        <v>158.82797065020776</v>
-      </c>
-      <c r="E47" s="28">
-        <f>E44*Inputs!D33</f>
-        <v>170.00548944207904</v>
-      </c>
-      <c r="F47" s="28">
-        <f>F44*Inputs!E33</f>
-        <v>180.24832043597254</v>
-      </c>
-      <c r="G47" s="28">
-        <f>G44*Inputs!F33</f>
-        <v>189.28326763301192</v>
-      </c>
-      <c r="H47" s="28">
-        <f>H44*Inputs!G33</f>
-        <v>196.85459833833241</v>
+        <v>96</v>
+      </c>
+      <c r="C47" s="29">
+        <f>C44*Inputs!B35</f>
+        <v>147.44791413258682</v>
+      </c>
+      <c r="D47" s="29">
+        <f>D44*Inputs!C35</f>
+        <v>159.31747166260379</v>
+      </c>
+      <c r="E47" s="29">
+        <f>E44*Inputs!D35</f>
+        <v>170.52943908932386</v>
+      </c>
+      <c r="F47" s="29">
+        <f>F44*Inputs!E35</f>
+        <v>180.80383805024977</v>
+      </c>
+      <c r="G47" s="29">
+        <f>G44*Inputs!F35</f>
+        <v>189.86663056812145</v>
+      </c>
+      <c r="H47" s="29">
+        <f>H44*Inputs!G35</f>
+        <v>197.46129579084632</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="28">
+        <v>97</v>
+      </c>
+      <c r="C48" s="29">
         <f t="shared" ref="C48:H48" si="12">C46-C47</f>
-        <v>469.29052713222336</v>
-      </c>
-      <c r="D48" s="28">
+        <v>482.93474984768795</v>
+      </c>
+      <c r="D48" s="29">
         <f t="shared" si="12"/>
-        <v>530.78854435744461</v>
-      </c>
-      <c r="E48" s="28">
+        <v>542.96826756068867</v>
+      </c>
+      <c r="E48" s="29">
         <f t="shared" si="12"/>
-        <v>593.53222183241746</v>
-      </c>
-      <c r="F48" s="28">
+        <v>603.82587235995277</v>
+      </c>
+      <c r="F48" s="29">
         <f t="shared" si="12"/>
-        <v>656.21168490415687</v>
-      </c>
-      <c r="G48" s="28">
+        <v>664.21702811516673</v>
+      </c>
+      <c r="G48" s="29">
         <f t="shared" si="12"/>
-        <v>717.37276412239316</v>
-      </c>
-      <c r="H48" s="28">
+        <v>722.7250868381426</v>
+      </c>
+      <c r="H48" s="29">
         <f t="shared" si="12"/>
-        <v>775.46688142835558</v>
+        <v>777.85683718983023</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="C49" s="28">
+        <v>116</v>
+      </c>
+      <c r="C49" s="29">
         <f>-MAX(C48,0)*Inputs!$B$10</f>
-        <v>-103.24391596908914</v>
-      </c>
-      <c r="D49" s="28">
+        <v>-106.24564496649135</v>
+      </c>
+      <c r="D49" s="29">
         <f>-MAX(D48,0)*Inputs!$B$10</f>
-        <v>-116.77347975863782</v>
-      </c>
-      <c r="E49" s="28">
+        <v>-119.4530188633515</v>
+      </c>
+      <c r="E49" s="29">
         <f>-MAX(E48,0)*Inputs!$B$10</f>
-        <v>-130.57708880313183</v>
-      </c>
-      <c r="F49" s="28">
+        <v>-132.8416919191896</v>
+      </c>
+      <c r="F49" s="29">
         <f>-MAX(F48,0)*Inputs!$B$10</f>
-        <v>-144.36657067891451</v>
-      </c>
-      <c r="G49" s="28">
+        <v>-146.12774618533669</v>
+      </c>
+      <c r="G49" s="29">
         <f>-MAX(G48,0)*Inputs!$B$10</f>
-        <v>-157.82200810692649</v>
-      </c>
-      <c r="H49" s="28">
+        <v>-158.99951910439137</v>
+      </c>
+      <c r="H49" s="29">
         <f>-MAX(H48,0)*Inputs!$B$10</f>
-        <v>-170.60271391423822</v>
+        <v>-171.12850418176265</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="28">
+        <v>100</v>
+      </c>
+      <c r="C50" s="29">
         <f t="shared" ref="C50:H50" si="13">C48+C49</f>
-        <v>366.04661116313423</v>
-      </c>
-      <c r="D50" s="28">
+        <v>376.68910488119661</v>
+      </c>
+      <c r="D50" s="29">
         <f t="shared" si="13"/>
-        <v>414.01506459880682</v>
-      </c>
-      <c r="E50" s="28">
+        <v>423.51524869733714</v>
+      </c>
+      <c r="E50" s="29">
         <f t="shared" si="13"/>
-        <v>462.95513302928566</v>
-      </c>
-      <c r="F50" s="28">
+        <v>470.98418044076317</v>
+      </c>
+      <c r="F50" s="29">
         <f t="shared" si="13"/>
-        <v>511.84511422524236</v>
-      </c>
-      <c r="G50" s="28">
+        <v>518.08928192983001</v>
+      </c>
+      <c r="G50" s="29">
         <f t="shared" si="13"/>
-        <v>559.55075601546673</v>
-      </c>
-      <c r="H50" s="28">
+        <v>563.72556773375118</v>
+      </c>
+      <c r="H50" s="29">
         <f t="shared" si="13"/>
-        <v>604.8641675141173</v>
+        <v>606.72833300806758</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C51" s="28">
-        <f>-C44*Inputs!B34</f>
-        <v>-240.44249292621225</v>
-      </c>
-      <c r="D51" s="28">
-        <f>-D44*Inputs!C34</f>
-        <v>-241.19236529902344</v>
-      </c>
-      <c r="E51" s="28">
-        <f>-E44*Inputs!D34</f>
-        <v>-238.25114989076457</v>
-      </c>
-      <c r="F51" s="28">
-        <f>-F44*Inputs!E34</f>
-        <v>-231.49076683863029</v>
-      </c>
-      <c r="G51" s="28">
-        <f>-G44*Inputs!F34</f>
-        <v>-220.92083635734863</v>
-      </c>
-      <c r="H51" s="28">
-        <f>-H44*Inputs!G34</f>
-        <v>-206.69732825524903</v>
+        <v>101</v>
+      </c>
+      <c r="C51" s="29">
+        <f>-C44*Inputs!B36</f>
+        <v>-241.18352640557103</v>
+      </c>
+      <c r="D51" s="29">
+        <f>-D44*Inputs!C36</f>
+        <v>-241.93570985296279</v>
+      </c>
+      <c r="E51" s="29">
+        <f>-E44*Inputs!D36</f>
+        <v>-238.98542974461284</v>
+      </c>
+      <c r="F51" s="29">
+        <f>-F44*Inputs!E36</f>
+        <v>-232.20421148105669</v>
+      </c>
+      <c r="G51" s="29">
+        <f>-G44*Inputs!F36</f>
+        <v>-221.60170492611269</v>
+      </c>
+      <c r="H51" s="29">
+        <f>-H44*Inputs!G36</f>
+        <v>-207.33436058038865</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="28">
-        <f>-Inputs!B35*(C44-B44)</f>
-        <v>-14.210787940418539</v>
-      </c>
-      <c r="D52" s="28">
-        <f>-Inputs!C35*(D44-C44)</f>
-        <v>-13.524580174850183</v>
-      </c>
-      <c r="E52" s="28">
-        <f>-Inputs!D35*(E44-D44)</f>
-        <v>-12.775299500171588</v>
-      </c>
-      <c r="F52" s="28">
-        <f>-Inputs!E35*(F44-E44)</f>
-        <v>-11.707001894892127</v>
-      </c>
-      <c r="G52" s="28">
-        <f>-Inputs!F35*(G44-F44)</f>
-        <v>-10.326456037305388</v>
-      </c>
-      <c r="H52" s="28">
-        <f>-Inputs!G35*(H44-G44)</f>
-        <v>-8.6536215394830904</v>
+        <v>102</v>
+      </c>
+      <c r="C52" s="29">
+        <f>-Inputs!B37*(C44-B44)</f>
+        <v>-14.728578947782347</v>
+      </c>
+      <c r="D52" s="29">
+        <f>-Inputs!C37*(D44-C44)</f>
+        <v>-13.566262352496324</v>
+      </c>
+      <c r="E52" s="29">
+        <f>-Inputs!D37*(E44-D44)</f>
+        <v>-12.814672426825478</v>
+      </c>
+      <c r="F52" s="29">
+        <f>-Inputs!E37*(F44-E44)</f>
+        <v>-11.743082374018135</v>
+      </c>
+      <c r="G52" s="29">
+        <f>-Inputs!F37*(G44-F44)</f>
+        <v>-10.358281733144935</v>
+      </c>
+      <c r="H52" s="29">
+        <f>-Inputs!G37*(H44-G44)</f>
+        <v>-8.6802916309482807</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C53" s="27">
+        <v>103</v>
+      </c>
+      <c r="C53" s="28">
         <f t="shared" ref="C53:H53" si="14">C50+C47+C51+C52</f>
-        <v>258.3882124892134</v>
-      </c>
-      <c r="D53" s="27">
+        <v>268.22491366043005</v>
+      </c>
+      <c r="D53" s="28">
         <f t="shared" si="14"/>
-        <v>318.12608977514088</v>
-      </c>
-      <c r="E53" s="27">
+        <v>327.33074815448185</v>
+      </c>
+      <c r="E53" s="28">
         <f t="shared" si="14"/>
-        <v>381.93417308042854</v>
-      </c>
-      <c r="F53" s="27">
+        <v>389.71351735864869</v>
+      </c>
+      <c r="F53" s="28">
         <f t="shared" si="14"/>
-        <v>448.89566592769251</v>
-      </c>
-      <c r="G53" s="27">
+        <v>454.94582612500494</v>
+      </c>
+      <c r="G53" s="28">
         <f t="shared" si="14"/>
-        <v>517.58673125382461</v>
-      </c>
-      <c r="H53" s="27">
+        <v>521.63221164261495</v>
+      </c>
+      <c r="H53" s="28">
         <f t="shared" si="14"/>
-        <v>586.36781605771762</v>
+        <v>588.17497658757691</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B54" s="28">
-        <f>NPV($G$7,$C$53:$H$53)*(1+$G$7)^(0.5*Inputs!$B$18)+IF(Inputs!$B$19=1,$H$50*(1+$H$7)*(1-$H$7/Inputs!$B$20),$H$53*(1+$H$7))/($G$7-$H$7)/(1+$G$7)^6</f>
-        <v>8291.5785174649227</v>
+        <v>141</v>
+      </c>
+      <c r="B54" s="29">
+        <f>SUMPRODUCT($C$53:$H$53,(1+$G$7)^(-DCF!$B$6:$G$6))-$C$53*Inputs!$B$20*(1+$G$7)^(-DCF!$B$6)+IF(Inputs!$B$21=1,$H$50*(1+$H$7)*(1-$H$7/Inputs!$B$22),$H$53*(1+$H$7))/($G$7-$H$7)/(1+$G$7)^(6-Inputs!$B$19)</f>
+        <v>8690.4121174954053</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B55" s="45">
         <f>(B54-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>186.22650630510276</v>
+        <v>187.21054962200435</v>
       </c>
     </row>
   </sheetData>
@@ -5569,646 +5740,1123 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:U40"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="5" width="14" customWidth="1"/>
-    <col min="6" max="12" width="12" customWidth="1"/>
+    <col min="6" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="J4" s="14" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+      <c r="M4" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="O4" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="U4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D5" s="18">
-        <v>13632.838656</v>
+        <v>13780.130816000001</v>
       </c>
       <c r="E5" s="18">
-        <v>14541.430656</v>
+        <v>15454.488815999999</v>
       </c>
       <c r="F5" s="19">
         <v>0.16687030338572639</v>
       </c>
       <c r="G5" s="19">
-        <v>8.6412895145026009E-2</v>
+        <v>8.9590047542978543E-2</v>
       </c>
       <c r="H5" s="47">
-        <v>0.9865370384127462</v>
+        <v>1.030727487313396</v>
       </c>
       <c r="I5" s="47">
-        <v>11.41654884675545</v>
+        <v>11.50493292035514</v>
       </c>
       <c r="J5" s="47">
-        <v>13.158521377462099</v>
+        <v>13.071592901785911</v>
       </c>
       <c r="K5" s="47">
-        <v>15.866667</v>
+        <v>16.038094999999998</v>
       </c>
       <c r="L5" s="47">
-        <v>12.168525000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13.01362244330315</v>
+      </c>
+      <c r="M5" s="47">
+        <v>0.96843879869313276</v>
+      </c>
+      <c r="N5" s="47">
+        <v>10.809669435977799</v>
+      </c>
+      <c r="O5" s="47">
+        <v>15.419607440967811</v>
+      </c>
+      <c r="P5" s="47">
+        <v>12.299997224466191</v>
+      </c>
+      <c r="Q5" s="19">
+        <v>5.3725183638773773E-2</v>
+      </c>
+      <c r="R5" s="19">
+        <v>0.25362690410176197</v>
+      </c>
+      <c r="S5" s="24">
+        <v>0.51310102488503084</v>
+      </c>
+      <c r="T5" s="19">
+        <v>3.2482420230748557E-2</v>
+      </c>
+      <c r="U5" s="19">
+        <v>4.4536817102137763E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D6" s="18">
-        <v>25835.502484802</v>
+        <v>26048.00866837598</v>
       </c>
       <c r="E6" s="18">
-        <v>24079.992110106941</v>
+        <v>23935.70899398423</v>
       </c>
       <c r="F6" s="19">
         <v>7.6307120679126594E-2</v>
       </c>
       <c r="G6" s="19">
-        <v>0.13394545265664581</v>
+        <v>0.1374906119736318</v>
       </c>
       <c r="H6" s="47">
-        <v>2.013034381288008</v>
+        <v>1.9217920088766289</v>
       </c>
       <c r="I6" s="47">
-        <v>15.02876239067403</v>
+        <v>13.977623499451679</v>
       </c>
       <c r="J6" s="47">
-        <v>16.860483336902981</v>
+        <v>15.453913189906009</v>
       </c>
       <c r="K6" s="47">
-        <v>21.518218999999998</v>
+        <v>21.609311999999999</v>
       </c>
       <c r="L6" s="47">
-        <v>33.322884000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+        <v>18.415495597796451</v>
+      </c>
+      <c r="M6" s="47">
+        <v>1.720090430346205</v>
+      </c>
+      <c r="N6" s="47">
+        <v>12.510602765198881</v>
+      </c>
+      <c r="O6" s="47">
+        <v>18.95162453591821</v>
+      </c>
+      <c r="P6" s="47">
+        <v>17.667091587113038</v>
+      </c>
+      <c r="Q6" s="19">
+        <v>5.9929054744048298E-2</v>
+      </c>
+      <c r="R6" s="19">
+        <v>7.27076634244741E-2</v>
+      </c>
+      <c r="S6" s="24">
+        <v>2.532813561932953</v>
+      </c>
+      <c r="T6" s="19">
+        <v>5.1555119272889652E-2</v>
+      </c>
+      <c r="U6" s="19">
+        <v>2.1662763466042151E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>180</v>
+        <v>199</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>181</v>
+        <v>200</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D7" s="18">
-        <v>11513.75956210681</v>
+        <v>11287.972468386601</v>
       </c>
       <c r="E7" s="18">
-        <v>11360.815559955319</v>
+        <v>10724.62857521624</v>
       </c>
       <c r="F7" s="19">
         <v>6.501521812647959E-2</v>
       </c>
       <c r="G7" s="19">
-        <v>7.7050091291577361E-2</v>
+        <v>7.973660454353769E-2</v>
       </c>
       <c r="H7" s="47">
-        <v>0.94347394713026911</v>
+        <v>0.86547246096654273</v>
       </c>
       <c r="I7" s="47">
-        <v>12.2449426251803</v>
+        <v>10.854142409512541</v>
       </c>
       <c r="J7" s="47">
-        <v>15.54399857703374</v>
+        <v>13.684116110082909</v>
       </c>
       <c r="K7" s="47">
-        <v>20.192307</v>
+        <v>19.717949000000001</v>
       </c>
       <c r="L7" s="47">
-        <v>16.649048000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16.229464150289271</v>
+      </c>
+      <c r="M7" s="47">
+        <v>0.7672280729902472</v>
+      </c>
+      <c r="N7" s="47">
+        <v>9.622030902649314</v>
+      </c>
+      <c r="O7" s="47">
+        <v>17.2808988764045</v>
+      </c>
+      <c r="P7" s="47">
+        <v>14.874274661508711</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>9.1674772807972982E-2</v>
+      </c>
+      <c r="R7" s="19">
+        <v>0.1617977528089887</v>
+      </c>
+      <c r="S7" s="24">
+        <v>1.003071048177602</v>
+      </c>
+      <c r="T7" s="19">
+        <v>3.2307484501766411E-2</v>
+      </c>
+      <c r="U7" s="19">
+        <v>2.3407022106631991E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>182</v>
+        <v>201</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D8" s="18">
-        <v>4448.7266819412234</v>
+        <v>4431.320817436218</v>
       </c>
       <c r="E8" s="18">
-        <v>7098.0861306335446</v>
+        <v>7335.7150149002073</v>
       </c>
       <c r="F8" s="19">
         <v>3.1860462339399209E-2</v>
       </c>
       <c r="G8" s="19">
-        <v>5.2709366004657691E-2</v>
+        <v>4.6504530550453567E-2</v>
       </c>
       <c r="H8" s="47">
-        <v>0.38071172956475202</v>
+        <v>0.38381819706498949</v>
       </c>
       <c r="I8" s="47">
-        <v>7.2228478242578413</v>
+        <v>8.2533506417956097</v>
       </c>
       <c r="J8" s="47">
-        <v>11.26240170656143</v>
+        <v>28.436837256688719</v>
       </c>
       <c r="K8" s="47"/>
       <c r="L8" s="47">
-        <v>9.011469</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+        <v>9.5657225893017799</v>
+      </c>
+      <c r="M8" s="47">
+        <v>0.36402650789103957</v>
+      </c>
+      <c r="N8" s="47">
+        <v>7.8277643830013712</v>
+      </c>
+      <c r="O8" s="47">
+        <v>11.77631688998177</v>
+      </c>
+      <c r="P8" s="47">
+        <v>8.9416127926028484</v>
+      </c>
+      <c r="Q8" s="19">
+        <v>3.8976447354534198E-2</v>
+      </c>
+      <c r="R8" s="19">
+        <v>0.3170238035496229</v>
+      </c>
+      <c r="S8" s="24">
+        <v>0.30173515307674631</v>
+      </c>
+      <c r="T8" s="19">
+        <v>2.0439845934196951E-2</v>
+      </c>
+      <c r="U8" s="19">
+        <v>4.8295454545454551E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>184</v>
+        <v>203</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D9" s="18">
-        <v>3375.2986701241002</v>
+        <v>3498.9186248196111</v>
       </c>
       <c r="E9" s="18">
-        <v>4534.4230264296993</v>
+        <v>4678.293940521572</v>
       </c>
       <c r="F9" s="19">
         <v>6.2273525721455503E-2</v>
       </c>
       <c r="G9" s="19">
-        <v>4.7920135312626982E-2</v>
+        <v>4.1526378731616007E-2</v>
       </c>
       <c r="H9" s="47">
-        <v>0.44823408026155398</v>
+        <v>0.44697838547588481</v>
       </c>
       <c r="I9" s="47">
-        <v>9.3537732591386096</v>
+        <v>10.76372173852903</v>
       </c>
       <c r="J9" s="47">
-        <v>12.78485650371664</v>
+        <v>15.13006660987371</v>
       </c>
       <c r="K9" s="47">
-        <v>40.163265000000003</v>
+        <v>41.469386999999998</v>
       </c>
       <c r="L9" s="47">
-        <v>16.131146999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.398886115854459</v>
+      </c>
+      <c r="M9" s="47">
+        <v>0.41122156710019198</v>
+      </c>
+      <c r="N9" s="47">
+        <v>9.9026589763077393</v>
+      </c>
+      <c r="O9" s="47">
+        <v>12.9015873015873</v>
+      </c>
+      <c r="P9" s="47">
+        <v>9.6992840095465382</v>
+      </c>
+      <c r="Q9" s="19">
+        <v>6.8865723335538531E-2</v>
+      </c>
+      <c r="R9" s="19">
+        <v>0.33015873015873032</v>
+      </c>
+      <c r="S9" s="24">
+        <v>0.3149662621628993</v>
+      </c>
+      <c r="T9" s="19">
+        <v>6.8680899116088684E-2</v>
+      </c>
+      <c r="U9" s="19"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="11" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>187</v>
+        <v>206</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D10" s="18">
-        <v>3014.9347040691991</v>
+        <v>3021.293783352447</v>
       </c>
       <c r="E10" s="18">
-        <v>3354.279208842815</v>
+        <v>3199.7979811883702</v>
       </c>
       <c r="F10" s="19">
         <v>2.455730036752413E-2</v>
       </c>
       <c r="G10" s="19">
-        <v>7.7743355617153106E-2</v>
+        <v>7.9150252253745085E-2</v>
       </c>
       <c r="H10" s="47">
-        <v>0.57215510582096851</v>
+        <v>0.54231699154196489</v>
       </c>
       <c r="I10" s="47">
-        <v>7.3595370469798658</v>
+        <v>6.8517405327195844</v>
       </c>
       <c r="J10" s="47">
-        <v>14.51210613730356</v>
+        <v>11.965198388776921</v>
       </c>
       <c r="K10" s="47">
-        <v>13.483708999999999</v>
+        <v>13.492462</v>
       </c>
       <c r="L10" s="47">
-        <v>16.059702000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.992326946477769</v>
+      </c>
+      <c r="M10" s="47">
+        <v>0.5192624289754203</v>
+      </c>
+      <c r="N10" s="47">
+        <v>6.5604646124276984</v>
+      </c>
+      <c r="O10" s="47">
+        <v>11.699346405228759</v>
+      </c>
+      <c r="P10" s="47">
+        <v>10.75075075075075</v>
+      </c>
+      <c r="Q10" s="19">
+        <v>3.5386212956306513E-2</v>
+      </c>
+      <c r="R10" s="19">
+        <v>8.8235294117647189E-2</v>
+      </c>
+      <c r="S10" s="24">
+        <v>1.2457970539341461</v>
+      </c>
+      <c r="T10" s="19">
+        <v>9.5611257034853944E-2</v>
+      </c>
+      <c r="U10" s="19">
+        <v>3.0726256983240219E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="11" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D11" s="18">
-        <v>87661.789183999994</v>
+        <v>90498.891776000004</v>
       </c>
       <c r="E11" s="18">
-        <v>103401.78918399999</v>
+        <v>112906.891776</v>
       </c>
       <c r="F11" s="19">
         <v>3.3110000866376048E-2</v>
       </c>
       <c r="G11" s="19">
-        <v>0.16450888926160431</v>
+        <v>0.15654252093401869</v>
       </c>
       <c r="H11" s="47">
-        <v>1.445228859127567</v>
+        <v>1.594257236921252</v>
       </c>
       <c r="I11" s="47">
-        <v>8.7851110393757743</v>
+        <v>10.184180166570959</v>
       </c>
       <c r="J11" s="47">
-        <v>11.203865286578051</v>
+        <v>12.42760143373649</v>
       </c>
       <c r="K11" s="47">
-        <v>13.873668</v>
+        <v>14.322679000000001</v>
       </c>
       <c r="L11" s="47">
-        <v>13.302899</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13.81990326504989</v>
+      </c>
+      <c r="M11" s="47">
+        <v>1.5650662702643749</v>
+      </c>
+      <c r="N11" s="47">
+        <v>9.9977070825634478</v>
+      </c>
+      <c r="O11" s="47">
+        <v>14.20686156689152</v>
+      </c>
+      <c r="P11" s="47">
+        <v>13.681342487183739</v>
+      </c>
+      <c r="Q11" s="19">
+        <v>2.9501375933732369E-2</v>
+      </c>
+      <c r="R11" s="19">
+        <v>3.8411367904872762E-2</v>
+      </c>
+      <c r="S11" s="24">
+        <v>3.5978680320043308</v>
+      </c>
+      <c r="T11" s="19">
+        <v>6.6277054694173054E-2</v>
+      </c>
+      <c r="U11" s="19">
+        <v>4.250797024442083E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>190</v>
+        <v>209</v>
       </c>
       <c r="D12" s="18">
-        <v>250946.25098072749</v>
+        <v>257382.57583061131</v>
       </c>
       <c r="E12" s="18">
-        <v>250748.37967794409</v>
+        <v>239421.79054835709</v>
       </c>
       <c r="F12" s="19">
         <v>-2.6411859534796411E-2</v>
       </c>
       <c r="G12" s="19">
-        <v>0.11189784698950871</v>
+        <v>0.11471017410175451</v>
       </c>
       <c r="H12" s="47">
-        <v>1.1490747765293381</v>
+        <v>1.130521915485809</v>
       </c>
       <c r="I12" s="47">
-        <v>10.268962338811329</v>
+        <v>9.8554633391365201</v>
       </c>
       <c r="J12" s="47">
-        <v>15.676974012406919</v>
+        <v>14.608552955018681</v>
       </c>
       <c r="K12" s="47">
-        <v>21.412759999999999</v>
+        <v>21.90352</v>
       </c>
       <c r="L12" s="47">
-        <v>18.58192</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+        <v>20.18598736552498</v>
+      </c>
+      <c r="M12" s="47">
+        <v>1.096402635417133</v>
+      </c>
+      <c r="N12" s="47">
+        <v>9.5580243339580413</v>
+      </c>
+      <c r="O12" s="47">
+        <v>21.040292159485411</v>
+      </c>
+      <c r="P12" s="47">
+        <v>20.00021428801023</v>
+      </c>
+      <c r="Q12" s="19">
+        <v>2.8894960585701179E-2</v>
+      </c>
+      <c r="R12" s="19">
+        <v>5.2003336389185417E-2</v>
+      </c>
+      <c r="S12" s="24">
+        <v>3.8816715940023498</v>
+      </c>
+      <c r="T12" s="19">
+        <v>3.0250866751488279E-2</v>
+      </c>
+      <c r="U12" s="19">
+        <v>4.2261904761904757E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="F14" s="48">
-        <f t="shared" ref="F14:L14" si="0">IFERROR(AVERAGE(F5:F12),"")</f>
+        <f t="shared" ref="F14:U14" si="0">IFERROR(AVERAGE(F5:F12),"")</f>
         <v>5.4197758993911382E-2</v>
       </c>
       <c r="G14" s="48">
         <f t="shared" si="0"/>
-        <v>9.4023504034849992E-2</v>
+        <v>9.3156390078966991E-2</v>
       </c>
       <c r="H14" s="49">
         <f t="shared" si="0"/>
-        <v>0.99230623976690036</v>
+        <v>0.98948558545580845</v>
       </c>
       <c r="I14" s="49">
         <f t="shared" si="0"/>
-        <v>10.210060671396651</v>
+        <v>10.280644406008882</v>
       </c>
       <c r="J14" s="49">
         <f t="shared" si="0"/>
-        <v>13.875400867245677</v>
+        <v>15.597234855733667</v>
       </c>
       <c r="K14" s="49">
         <f t="shared" si="0"/>
-        <v>20.930084999999998</v>
+        <v>21.221914857142856</v>
       </c>
       <c r="L14" s="49">
         <f t="shared" si="0"/>
-        <v>16.903449250000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+        <v>14.077676059199719</v>
+      </c>
+      <c r="M14" s="49">
+        <f t="shared" si="0"/>
+        <v>0.92646708895971797</v>
+      </c>
+      <c r="N14" s="49">
+        <f t="shared" si="0"/>
+        <v>9.598615311510537</v>
+      </c>
+      <c r="O14" s="49">
+        <f t="shared" si="0"/>
+        <v>15.409566897058159</v>
+      </c>
+      <c r="P14" s="49">
+        <f t="shared" si="0"/>
+        <v>13.489320975147756</v>
+      </c>
+      <c r="Q14" s="48">
+        <f t="shared" si="0"/>
+        <v>5.086921641957598E-2</v>
+      </c>
+      <c r="R14" s="48">
+        <f t="shared" si="0"/>
+        <v>0.16424560655691042</v>
+      </c>
+      <c r="S14" s="50">
+        <f t="shared" si="0"/>
+        <v>1.6738779662720076</v>
+      </c>
+      <c r="T14" s="48">
+        <f t="shared" si="0"/>
+        <v>4.9700618442025696E-2</v>
+      </c>
+      <c r="U14" s="48">
+        <f t="shared" si="0"/>
+        <v>3.6199741315690322E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F15" s="40">
-        <f t="shared" ref="F15:L15" si="1">IFERROR(MEDIAN(F5:F12),"")</f>
+        <f t="shared" ref="F15:U15" si="1">IFERROR(MEDIAN(F5:F12),"")</f>
         <v>4.7691763293915779E-2</v>
       </c>
       <c r="G15" s="40">
         <f t="shared" si="1"/>
-        <v>8.2078125381089551E-2</v>
-      </c>
-      <c r="H15" s="50">
+        <v>8.4663326043258116E-2</v>
+      </c>
+      <c r="H15" s="51">
         <f t="shared" si="1"/>
-        <v>0.96500549277150771</v>
-      </c>
-      <c r="I15" s="50">
+        <v>0.94809997413996938</v>
+      </c>
+      <c r="I15" s="51">
         <f t="shared" si="1"/>
-        <v>9.8113677989749704</v>
-      </c>
-      <c r="J15" s="50">
+        <v>10.473950952549995</v>
+      </c>
+      <c r="J15" s="51">
         <f t="shared" si="1"/>
-        <v>13.83531375738283</v>
-      </c>
-      <c r="K15" s="50">
+        <v>14.146334532550796</v>
+      </c>
+      <c r="K15" s="51">
         <f t="shared" si="1"/>
-        <v>20.192307</v>
-      </c>
-      <c r="L15" s="50">
+        <v>19.717949000000001</v>
+      </c>
+      <c r="L15" s="51">
         <f t="shared" si="1"/>
-        <v>16.0954245</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+        <v>13.41676285417652</v>
+      </c>
+      <c r="M15" s="51">
+        <f t="shared" si="1"/>
+        <v>0.86783343584168993</v>
+      </c>
+      <c r="N15" s="51">
+        <f t="shared" si="1"/>
+        <v>9.7623449394785276</v>
+      </c>
+      <c r="O15" s="51">
+        <f t="shared" si="1"/>
+        <v>14.813234503929666</v>
+      </c>
+      <c r="P15" s="51">
+        <f t="shared" si="1"/>
+        <v>12.990669855824965</v>
+      </c>
+      <c r="Q15" s="40">
+        <f t="shared" si="1"/>
+        <v>4.6350815496653985E-2</v>
+      </c>
+      <c r="R15" s="40">
+        <f t="shared" si="1"/>
+        <v>0.12501652346331793</v>
+      </c>
+      <c r="S15" s="45">
+        <f t="shared" si="1"/>
+        <v>1.1244340510558741</v>
+      </c>
+      <c r="T15" s="40">
+        <f t="shared" si="1"/>
+        <v>4.2018769751819104E-2</v>
+      </c>
+      <c r="U15" s="40">
+        <f t="shared" si="1"/>
+        <v>4.2261904761904757E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="F16" s="40">
-        <f t="shared" ref="F16:L16" si="2">IFERROR(QUARTILE(F5:F12,1),"")</f>
+        <f t="shared" ref="F16:U16" si="2">IFERROR(QUARTILE(F5:F12,1),"")</f>
         <v>3.0034671846430439E-2</v>
       </c>
       <c r="G16" s="40">
         <f t="shared" si="2"/>
-        <v>7.0964909969847445E-2</v>
-      </c>
-      <c r="H16" s="50">
+        <v>7.0988821827922211E-2</v>
+      </c>
+      <c r="H16" s="51">
         <f t="shared" si="2"/>
-        <v>0.54117484943111482</v>
-      </c>
-      <c r="I16" s="50">
+        <v>0.51848234002544491</v>
+      </c>
+      <c r="I16" s="51">
         <f t="shared" si="2"/>
-        <v>8.4287175412767965</v>
-      </c>
-      <c r="J16" s="50">
+        <v>9.4549351648012916</v>
+      </c>
+      <c r="J16" s="51">
         <f t="shared" si="2"/>
-        <v>12.404242804427838</v>
-      </c>
-      <c r="K16" s="50">
+        <v>12.910595034773555</v>
+      </c>
+      <c r="K16" s="51">
         <f t="shared" si="2"/>
-        <v>14.870167500000001</v>
-      </c>
-      <c r="L16" s="50">
+        <v>15.180387</v>
+      </c>
+      <c r="L16" s="51">
         <f t="shared" si="2"/>
-        <v>13.0193055</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+        <v>10.843966738821942</v>
+      </c>
+      <c r="M16" s="51">
+        <f t="shared" si="2"/>
+        <v>0.49225221350661319</v>
+      </c>
+      <c r="N16" s="51">
+        <f t="shared" si="2"/>
+        <v>9.1254593462188733</v>
+      </c>
+      <c r="O16" s="51">
+        <f t="shared" si="2"/>
+        <v>12.620269698685917</v>
+      </c>
+      <c r="P16" s="51">
+        <f t="shared" si="2"/>
+        <v>10.487884065449698</v>
+      </c>
+      <c r="Q16" s="40">
+        <f t="shared" si="2"/>
+        <v>3.3915003700662978E-2</v>
+      </c>
+      <c r="R16" s="40">
+        <f t="shared" si="2"/>
+        <v>6.753158166565193E-2</v>
+      </c>
+      <c r="S16" s="45">
+        <f t="shared" si="2"/>
+        <v>0.46356733420449797</v>
+      </c>
+      <c r="T16" s="40">
+        <f t="shared" si="2"/>
+        <v>3.1793330064196879E-2</v>
+      </c>
+      <c r="U16" s="40">
+        <f t="shared" si="2"/>
+        <v>2.7066639544936107E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="F17" s="40">
-        <f t="shared" ref="F17:L17" si="3">IFERROR(QUARTILE(F5:F12,3),"")</f>
+        <f t="shared" ref="F17:U17" si="3">IFERROR(QUARTILE(F5:F12,3),"")</f>
         <v>6.7838193764641341E-2</v>
       </c>
       <c r="G17" s="40">
         <f t="shared" si="3"/>
-        <v>0.11740974840629298</v>
-      </c>
-      <c r="H17" s="50">
+        <v>0.12040528356972383</v>
+      </c>
+      <c r="H17" s="51">
         <f t="shared" si="3"/>
-        <v>1.2231132971788954</v>
-      </c>
-      <c r="I17" s="50">
+        <v>1.2464557458446697</v>
+      </c>
+      <c r="I17" s="51">
         <f t="shared" si="3"/>
-        <v>11.623647291361664</v>
-      </c>
-      <c r="J17" s="50">
+        <v>11.01684003722319</v>
+      </c>
+      <c r="J17" s="51">
         <f t="shared" si="3"/>
-        <v>15.577242435877036</v>
-      </c>
-      <c r="K17" s="50">
+        <v>15.211028254881786</v>
+      </c>
+      <c r="K17" s="51">
         <f t="shared" si="3"/>
-        <v>21.465489499999997</v>
-      </c>
-      <c r="L17" s="50">
+        <v>21.756416000000002</v>
+      </c>
+      <c r="L17" s="51">
         <f t="shared" si="3"/>
-        <v>17.132266000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+        <v>16.775972012166065</v>
+      </c>
+      <c r="M17" s="51">
+        <f t="shared" si="3"/>
+        <v>1.2135685441289434</v>
+      </c>
+      <c r="N17" s="51">
+        <f t="shared" si="3"/>
+        <v>10.200697670917036</v>
+      </c>
+      <c r="O17" s="51">
+        <f t="shared" si="3"/>
+        <v>17.698580291282926</v>
+      </c>
+      <c r="P17" s="51">
+        <f t="shared" si="3"/>
+        <v>15.572478892909793</v>
+      </c>
+      <c r="Q17" s="40">
+        <f t="shared" si="3"/>
+        <v>6.2163221891920854E-2</v>
+      </c>
+      <c r="R17" s="40">
+        <f t="shared" si="3"/>
+        <v>0.26947612896372719</v>
+      </c>
+      <c r="S17" s="45">
+        <f t="shared" si="3"/>
+        <v>2.7990771794507974</v>
+      </c>
+      <c r="T17" s="40">
+        <f t="shared" si="3"/>
+        <v>6.6878015799651969E-2</v>
+      </c>
+      <c r="U17" s="40">
+        <f t="shared" si="3"/>
+        <v>4.35223936732793E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="B21" s="28">
+        <v>221</v>
+      </c>
+      <c r="B21" s="29">
         <f>(Inputs!$B$5*Inputs!$B$6)*Inputs!$B$7</f>
-        <v>4828.6452455999997</v>
+        <v>4966.8387964000003</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="E21" s="29">
+        <v>180</v>
+      </c>
+      <c r="E21" s="30">
         <f>IF(B23&lt;=0,"n.m.",B22/B23)</f>
-        <v>1.4072557092042248</v>
-      </c>
-      <c r="F21" s="29">
+        <v>1.4848590736497047</v>
+      </c>
+      <c r="F21" s="30">
         <f>H15</f>
-        <v>0.96500549277150771</v>
+        <v>0.94809997413996938</v>
       </c>
       <c r="G21" s="41">
         <f>IF(B23&lt;=0,"",(H15*B23-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>75.88009494503217</v>
-      </c>
-      <c r="H21" s="34">
+        <v>68.410125103408859</v>
+      </c>
+      <c r="H21" s="35">
         <f>IF(G21="","",G21/Inputs!$B$5-1)</f>
-        <v>-0.36127866207885373</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-0.44017900897374096</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B22" s="28">
+        <v>141</v>
+      </c>
+      <c r="B22" s="29">
         <f>B21+Inputs!$B$8+Inputs!$B$9</f>
-        <v>5551.0172456</v>
+        <v>6048.0477964000002</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="E22" s="29">
+        <v>181</v>
+      </c>
+      <c r="E22" s="30">
         <f>IF(B24&lt;=0,"n.m.",B22/B24)</f>
-        <v>11.447929089466596</v>
-      </c>
-      <c r="F22" s="29">
+        <v>11.874442747609255</v>
+      </c>
+      <c r="F22" s="30">
         <f>I15</f>
-        <v>9.8113677989749704</v>
+        <v>10.473950952549995</v>
       </c>
       <c r="G22" s="41">
         <f>IF(B24&lt;=0,"",(I15*B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>99.275988191116852</v>
-      </c>
-      <c r="H22" s="34">
+        <v>104.65013877329928</v>
+      </c>
+      <c r="H22" s="35">
         <f>IF(G22="","",G22/Inputs!$B$5-1)</f>
-        <v>-0.16434353374480759</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-0.14361588565221539</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B23" s="31">
-        <f>Historicals!E5</f>
-        <v>3944.569</v>
+        <v>222</v>
+      </c>
+      <c r="B23" s="18">
+        <v>4073.1460000000002</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="E23" s="29">
+        <v>182</v>
+      </c>
+      <c r="E23" s="30">
         <f>IF(B25&lt;=0,"n.m.",B22/B25)</f>
-        <v>16.206038944003645</v>
-      </c>
-      <c r="F23" s="29">
+        <v>15.756779970870198</v>
+      </c>
+      <c r="F23" s="30">
         <f>J15</f>
-        <v>13.83531375738283</v>
+        <v>14.146334532550796</v>
       </c>
       <c r="G23" s="41">
         <f>IF(B25&lt;=0,"",(J15*B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
-        <v>98.821261927672992</v>
-      </c>
-      <c r="H23" s="34">
+        <v>106.9915518733432</v>
+      </c>
+      <c r="H23" s="35">
         <f>IF(G23="","",G23/Inputs!$B$5-1)</f>
-        <v>-0.16817119589500851</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+        <v>-0.12445538565185599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B24" s="31">
-        <f>Historicals!E9</f>
-        <v>484.89270000000005</v>
+        <v>223</v>
+      </c>
+      <c r="B24" s="18">
+        <v>509.33318935052228</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="E24" s="29">
+        <v>183</v>
+      </c>
+      <c r="E24" s="30">
         <f>IF(B26&lt;=0,"n.m.",(Inputs!$B$5*Inputs!$B$6)/B26)</f>
-        <v>21.063829787234042</v>
-      </c>
-      <c r="F24" s="29">
+        <v>19.123630672926449</v>
+      </c>
+      <c r="F24" s="30">
         <f>K15</f>
-        <v>20.192307</v>
+        <v>19.717949000000001</v>
       </c>
       <c r="G24" s="41">
         <f>IF(B26&lt;=0,"",K15*B26/Inputs!$B$6)</f>
-        <v>113.88461147999999</v>
-      </c>
-      <c r="H24" s="34">
+        <v>125.99769411</v>
+      </c>
+      <c r="H24" s="35">
         <f>IF(G24="","",G24/Inputs!$B$5-1)</f>
-        <v>-4.1375324242424294E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+        <v>3.1077693207856028E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>205</v>
-      </c>
-      <c r="B25" s="31">
-        <f>Historicals!E14</f>
-        <v>342.52770000000015</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+        <v>224</v>
+      </c>
+      <c r="B25" s="18">
+        <v>383.83780236705212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B26" s="4">
-        <f>Historicals!E23</f>
-        <v>5.64</v>
+        <v>225</v>
+      </c>
+      <c r="B26" s="24">
+        <v>6.39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A28" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A30" s="9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B31" s="24">
+        <v>3.6360024567825628</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" s="24">
+        <v>67.942656628023798</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B33" s="24">
+        <v>34.226876356969598</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="B34" s="24">
+        <v>0.61080478562092932</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="B35" s="24">
+        <v>1.5729610088763399</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B36" s="22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="B37" s="19">
+        <v>6.0522733984546662E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="35">
+        <f>IF(B23&gt;0,B24/B23,0)</f>
+        <v>0.12504663209973868</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" s="51">
+        <f>B31+B32*B37+B33*B38</f>
+        <v>12.028033405817066</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40" s="45">
+        <f>IF(B24&lt;=0,"",(B39*B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6)</f>
+        <v>124.12467727892022</v>
       </c>
     </row>
   </sheetData>
@@ -6218,7 +6866,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6227,136 +6875,153 @@
   <sheetData>
     <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>208</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>209</v>
+        <v>241</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>212</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B5" s="23">
+        <v>245</v>
+      </c>
+      <c r="B5" s="24">
         <v>112</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="24">
         <v>154.6</v>
       </c>
       <c r="D5" s="41">
-        <f>IFERROR(C5-B5,"")</f>
+        <f t="shared" ref="D5:D10" si="0">IFERROR(C5-B5,"")</f>
         <v>42.599999999999994</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="11" t="s">
-        <v>214</v>
+        <v>246</v>
       </c>
       <c r="B6" s="41">
         <f>MIN(DCF!D40:F42)</f>
-        <v>112.18979017657526</v>
+        <v>110.24282513046317</v>
       </c>
       <c r="C6" s="41">
         <f>MAX(DCF!D40:F42)</f>
-        <v>145.01137554243135</v>
+        <v>144.10029021035498</v>
       </c>
       <c r="D6" s="41">
-        <f>IFERROR(C6-B6,"")</f>
-        <v>32.821585365856095</v>
+        <f t="shared" si="0"/>
+        <v>33.85746507989181</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>215</v>
+        <v>247</v>
       </c>
       <c r="B7" s="41">
         <f>(Peers!I16*Peers!B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>82.781109499011663</v>
+        <v>91.880634713441381</v>
       </c>
       <c r="C7" s="41">
         <f>(Peers!I17*Peers!B24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>120.89630049834823</v>
+        <v>111.45319762099643</v>
       </c>
       <c r="D7" s="41">
-        <f>IFERROR(C7-B7,"")</f>
-        <v>38.115190999336562</v>
+        <f t="shared" si="0"/>
+        <v>19.572562907555053</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="11" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="B8" s="41">
         <f>(Peers!J16*Peers!B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>86.761242532191645</v>
+        <v>95.321687373234155</v>
       </c>
       <c r="C8" s="41">
         <f>(Peers!J17*Peers!B25-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
-        <v>113.50096289205001</v>
+        <v>117.04612364681832</v>
       </c>
       <c r="D8" s="41">
-        <f>IFERROR(C8-B8,"")</f>
-        <v>26.739720359858367</v>
+        <f t="shared" si="0"/>
+        <v>21.724436273584161</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="11" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="B9" s="41">
         <f>Peers!K16*Peers!B26/Inputs!$B$6</f>
-        <v>83.867744700000003</v>
+        <v>97.002672929999989</v>
       </c>
       <c r="C9" s="41">
         <f>Peers!K17*Peers!B26/Inputs!$B$6</f>
-        <v>121.06536077999998</v>
+        <v>139.02349824000001</v>
       </c>
       <c r="D9" s="41">
-        <f>IFERROR(C9-B9,"")</f>
-        <v>37.197616079999975</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="4">
-        <f>Inputs!$B$5</f>
-        <v>118.8</v>
+        <f t="shared" si="0"/>
+        <v>42.020825310000021</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B10" s="41">
+        <f>((Peers!$B$39-Peers!$B$35)*Peers!$B$24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
+        <v>104.41356756861812</v>
+      </c>
+      <c r="C10" s="41">
+        <f>((Peers!$B$39+Peers!$B$35)*Peers!$B$24-Inputs!$B$8-Inputs!$B$9)/Inputs!$B$7/Inputs!$B$6</f>
+        <v>143.8357869892223</v>
+      </c>
+      <c r="D10" s="41">
+        <f t="shared" si="0"/>
+        <v>39.422219420604179</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="51">
-        <f>DCF!$B$30</f>
-        <v>130</v>
+        <v>146</v>
+      </c>
+      <c r="B12" s="4">
+        <f>Inputs!$B$5</f>
+        <v>122.2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="52">
+        <f>DCF!$B$30</f>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="52" t="str">
+      <c r="B14" s="53" t="str">
         <f>DCF!$B$33</f>
-        <v>BUY</v>
+        <v>HOLD</v>
       </c>
     </row>
   </sheetData>
